--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25F8D59-D3F6-4523-89CC-3ED5A2BA798F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F719E47B-1EB1-476F-A0A1-DEA1E5F2B676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="168">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -509,6 +509,27 @@
   </si>
   <si>
     <t>PTA19_IMPERIUS</t>
+  </si>
+  <si>
+    <t>extremes_fractals</t>
+  </si>
+  <si>
+    <t>чистить дбшки через проверку наличия в wss</t>
+  </si>
+  <si>
+    <t>Индикатор зебры (%-ый ход)</t>
+  </si>
+  <si>
+    <t>Проверка исполнения таблице сделок</t>
+  </si>
+  <si>
+    <t>Изучить все индикаторы, которые сейчас есть в проекте</t>
+  </si>
+  <si>
+    <t>Создать таблицу анализа действий Qtrader. Выяснить причину лишних сделок</t>
+  </si>
+  <si>
+    <t>Дописать новые батники</t>
   </si>
 </sst>
 </file>
@@ -1015,6 +1036,12 @@
       <c r="O2" s="2" t="s">
         <v>152</v>
       </c>
+      <c r="P2" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="R2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1047,11 +1074,14 @@
       <c r="L3" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>127</v>
+      <c r="O3" s="12" t="s">
+        <v>166</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>144</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>107</v>
@@ -1082,8 +1112,8 @@
       <c r="L4" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="O4" s="2" t="s">
-        <v>126</v>
+      <c r="O4" s="4" t="s">
+        <v>167</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>131</v>
@@ -1188,7 +1218,7 @@
         <v>132</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>69</v>
@@ -1252,7 +1282,7 @@
         <v>141</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>130</v>
@@ -1280,7 +1310,7 @@
       <c r="L10" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="O10" s="4" t="s">
         <v>153</v>
       </c>
       <c r="R10" s="2" t="s">
@@ -1367,7 +1397,7 @@
       <c r="L13" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="O13" s="12" t="s">
+      <c r="O13" s="4" t="s">
         <v>157</v>
       </c>
       <c r="R13" s="2" t="s">
@@ -1416,8 +1446,11 @@
       <c r="L15" s="7" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="O15" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1429,6 +1462,9 @@
       </c>
       <c r="E16" s="7" t="s">
         <v>92</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="30" x14ac:dyDescent="0.25">
@@ -1444,8 +1480,11 @@
       <c r="E17" s="4" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O17" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1457,6 +1496,9 @@
       </c>
       <c r="E18" s="7" t="s">
         <v>94</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F719E47B-1EB1-476F-A0A1-DEA1E5F2B676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6303A8D-207B-46F3-8E02-D046A319D820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="175">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -530,6 +530,27 @@
   </si>
   <si>
     <t>Дописать новые батники</t>
+  </si>
+  <si>
+    <t>Робот с фильтрацией направления по ZZ</t>
+  </si>
+  <si>
+    <t>ST1 на PZZ</t>
+  </si>
+  <si>
+    <t>STA3</t>
+  </si>
+  <si>
+    <t>Определение лучших и худших параметров при оптимизации</t>
+  </si>
+  <si>
+    <t>Q-обучение для генерации стратегий (создать набор флагов по типу "выше_BB")</t>
+  </si>
+  <si>
+    <t>STA3_LITE</t>
+  </si>
+  <si>
+    <t>STA3_FORCE</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1023,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1033,11 +1054,8 @@
       <c r="L2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>163</v>
+      <c r="O2" s="12" t="s">
+        <v>166</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>165</v>
@@ -1049,7 +1067,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1074,11 +1092,8 @@
       <c r="L3" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="O3" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>144</v>
+      <c r="O3" s="4" t="s">
+        <v>167</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>154</v>
@@ -1113,10 +1128,10 @@
         <v>114</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>106</v>
@@ -1125,7 +1140,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1145,10 +1160,10 @@
         <v>115</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>137</v>
+        <v>142</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>51</v>
@@ -1180,10 +1195,10 @@
         <v>110</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>138</v>
+        <v>153</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>76</v>
@@ -1192,7 +1207,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1214,11 +1229,11 @@
       <c r="L7" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>127</v>
+      <c r="O7" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>69</v>
@@ -1227,7 +1242,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1247,10 +1262,10 @@
         <v>118</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>120</v>
+        <v>172</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>70</v>
@@ -1278,11 +1293,11 @@
       <c r="L9" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="O9" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>126</v>
+      <c r="O9" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>130</v>
@@ -1291,7 +1306,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1311,7 +1326,10 @@
         <v>122</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>153</v>
+        <v>162</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>133</v>
@@ -1339,8 +1357,8 @@
       <c r="L11" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="O11" s="2" t="s">
-        <v>155</v>
+      <c r="Q11" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>134</v>
@@ -1349,7 +1367,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1368,8 +1386,8 @@
       <c r="L12" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="O12" s="2" t="s">
-        <v>156</v>
+      <c r="Q12" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>135</v>
@@ -1397,14 +1415,14 @@
       <c r="L13" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="O13" s="4" t="s">
-        <v>157</v>
+      <c r="Q13" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1423,8 +1441,8 @@
       <c r="L14" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="O14" s="2" t="s">
-        <v>158</v>
+      <c r="Q14" s="2" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
@@ -1446,11 +1464,11 @@
       <c r="L15" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="O15" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q15" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1463,11 +1481,11 @@
       <c r="E16" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="O16" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q16" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1480,11 +1498,11 @@
       <c r="E17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="O17" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q17" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1497,11 +1515,11 @@
       <c r="E18" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="O18" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q18" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1515,10 +1533,13 @@
         <v>95</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1531,11 +1552,14 @@
       <c r="E20" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="O20" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O20" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1546,10 +1570,13 @@
         <v>97</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1560,10 +1587,13 @@
         <v>98</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1573,8 +1603,11 @@
       <c r="E23" s="7" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O23" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1584,8 +1617,11 @@
       <c r="E24" s="7" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O24" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1595,8 +1631,11 @@
       <c r="E25" s="7" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O25" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1606,8 +1645,11 @@
       <c r="E26" s="7" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O26" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1615,7 +1657,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1623,7 +1665,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1631,7 +1673,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1639,7 +1681,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1647,7 +1689,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6303A8D-207B-46F3-8E02-D046A319D820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC3B3FF-6FFF-4F17-B572-4ED36EEE5C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="178">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -551,6 +551,15 @@
   </si>
   <si>
     <t>STA3_FORCE</t>
+  </si>
+  <si>
+    <t>Пересмотреть sgs</t>
+  </si>
+  <si>
+    <t>Смотреть результаты заявок в QT и от этого отталкиваться</t>
+  </si>
+  <si>
+    <t>Генетические алгоритмы для создания стратегий</t>
   </si>
 </sst>
 </file>
@@ -1054,7 +1063,7 @@
       <c r="L2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="O2" s="4" t="s">
         <v>166</v>
       </c>
       <c r="Q2" s="2" t="s">
@@ -1242,7 +1251,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1261,8 +1270,8 @@
       <c r="L8" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="O8" s="2" t="s">
-        <v>172</v>
+      <c r="O8" s="12" t="s">
+        <v>177</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>155</v>
@@ -1357,6 +1366,9 @@
       <c r="L11" s="4" t="s">
         <v>124</v>
       </c>
+      <c r="O11" s="2" t="s">
+        <v>175</v>
+      </c>
       <c r="Q11" s="2" t="s">
         <v>164</v>
       </c>
@@ -1386,6 +1398,9 @@
       <c r="L12" s="4" t="s">
         <v>125</v>
       </c>
+      <c r="O12" s="12" t="s">
+        <v>176</v>
+      </c>
       <c r="Q12" s="2" t="s">
         <v>139</v>
       </c>
@@ -1420,6 +1435,9 @@
       </c>
       <c r="R13" s="2" t="s">
         <v>136</v>
+      </c>
+      <c r="S13" s="9" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="90" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC3B3FF-6FFF-4F17-B572-4ED36EEE5C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C5C295-1704-4B0A-A530-565FFF1875AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="180">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -560,6 +560,12 @@
   </si>
   <si>
     <t>Генетические алгоритмы для создания стратегий</t>
+  </si>
+  <si>
+    <t>GLTA</t>
+  </si>
+  <si>
+    <t>Реализовать нейронку с дискретными фичами, как цель выбрать результат фейк-бота по зигзагу</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +1276,7 @@
       <c r="L8" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="O8" s="12" t="s">
+      <c r="O8" s="4" t="s">
         <v>177</v>
       </c>
       <c r="Q8" s="2" t="s">
@@ -1411,7 +1417,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1429,6 +1435,9 @@
       </c>
       <c r="L13" s="4" t="s">
         <v>121</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>179</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>163</v>
@@ -1673,6 +1682,9 @@
       </c>
       <c r="D27" s="7" t="s">
         <v>62</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C5C295-1704-4B0A-A530-565FFF1875AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D5C61B-CA0F-41CE-B8AF-584D7EDA1D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,17 +16,26 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Идеи" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="184">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -520,9 +529,6 @@
     <t>Индикатор зебры (%-ый ход)</t>
   </si>
   <si>
-    <t>Проверка исполнения таблице сделок</t>
-  </si>
-  <si>
     <t>Изучить все индикаторы, которые сейчас есть в проекте</t>
   </si>
   <si>
@@ -566,6 +572,21 @@
   </si>
   <si>
     <t>Реализовать нейронку с дискретными фичами, как цель выбрать результат фейк-бота по зигзагу</t>
+  </si>
+  <si>
+    <t>Пересмотреть политику закрытия сделок VT в 18:26</t>
+  </si>
+  <si>
+    <t>Сделать разные критерии оценки Эвол. Моделей</t>
+  </si>
+  <si>
+    <t>PTA20_HANZO</t>
+  </si>
+  <si>
+    <t>PTA20_HOGGER</t>
+  </si>
+  <si>
+    <t>Добавить группы параметров к эвол. Моделям</t>
   </si>
 </sst>
 </file>
@@ -1070,10 +1091,13 @@
         <v>54</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>174</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>5</v>
@@ -1108,7 +1132,10 @@
         <v>116</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>179</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>154</v>
@@ -1145,6 +1172,9 @@
       <c r="O4" s="4" t="s">
         <v>123</v>
       </c>
+      <c r="P4" s="9" t="s">
+        <v>175</v>
+      </c>
       <c r="Q4" s="2" t="s">
         <v>132</v>
       </c>
@@ -1177,6 +1207,9 @@
       <c r="O5" s="4" t="s">
         <v>142</v>
       </c>
+      <c r="P5" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="Q5" s="2" t="s">
         <v>140</v>
       </c>
@@ -1187,7 +1220,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1212,6 +1245,9 @@
       <c r="O6" s="4" t="s">
         <v>153</v>
       </c>
+      <c r="P6" s="4" t="s">
+        <v>152</v>
+      </c>
       <c r="Q6" s="2" t="s">
         <v>141</v>
       </c>
@@ -1222,7 +1258,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1247,8 +1283,11 @@
       <c r="O7" s="4" t="s">
         <v>157</v>
       </c>
+      <c r="P7" s="2" t="s">
+        <v>183</v>
+      </c>
       <c r="Q7" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>69</v>
@@ -1277,10 +1316,10 @@
         <v>118</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>70</v>
@@ -1312,7 +1351,7 @@
         <v>161</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>130</v>
@@ -1321,7 +1360,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1344,7 +1383,7 @@
         <v>162</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>133</v>
@@ -1372,11 +1411,11 @@
       <c r="L11" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="O11" s="2" t="s">
-        <v>175</v>
+      <c r="O11" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>134</v>
@@ -1385,7 +1424,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1404,11 +1443,11 @@
       <c r="L12" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="O12" s="12" t="s">
-        <v>176</v>
+      <c r="O12" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>135</v>
@@ -1417,7 +1456,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1436,20 +1475,20 @@
       <c r="L13" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="O13" s="12" t="s">
-        <v>179</v>
+      <c r="O13" s="7" t="s">
+        <v>146</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>136</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="90" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1468,11 +1507,17 @@
       <c r="L14" s="4" t="s">
         <v>147</v>
       </c>
+      <c r="O14" s="7" t="s">
+        <v>159</v>
+      </c>
       <c r="Q14" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1491,11 +1536,14 @@
       <c r="L15" s="7" t="s">
         <v>148</v>
       </c>
+      <c r="O15" s="7" t="s">
+        <v>160</v>
+      </c>
       <c r="Q15" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1508,8 +1556,14 @@
       <c r="E16" s="7" t="s">
         <v>92</v>
       </c>
+      <c r="O16" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>181</v>
+      </c>
       <c r="Q16" s="2" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="30" x14ac:dyDescent="0.25">
@@ -1525,8 +1579,14 @@
       <c r="E17" s="4" t="s">
         <v>93</v>
       </c>
+      <c r="O17" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>182</v>
+      </c>
       <c r="Q17" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -1542,11 +1602,14 @@
       <c r="E18" s="7" t="s">
         <v>94</v>
       </c>
+      <c r="O18" s="7" t="s">
+        <v>173</v>
+      </c>
       <c r="Q18" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1560,13 +1623,13 @@
         <v>95</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1579,14 +1642,11 @@
       <c r="E20" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="O20" s="4" t="s">
-        <v>145</v>
-      </c>
       <c r="Q20" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1596,14 +1656,8 @@
       <c r="E21" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="O21" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1612,12 +1666,6 @@
       </c>
       <c r="E22" s="7" t="s">
         <v>98</v>
-      </c>
-      <c r="O22" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -1630,9 +1678,6 @@
       <c r="E23" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="O23" s="7" t="s">
-        <v>160</v>
-      </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
@@ -1644,9 +1689,6 @@
       <c r="E24" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="O24" s="4" t="s">
-        <v>170</v>
-      </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
@@ -1658,9 +1700,6 @@
       <c r="E25" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="O25" s="7" t="s">
-        <v>173</v>
-      </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
@@ -1672,9 +1711,6 @@
       <c r="E26" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="O26" s="7" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -1682,9 +1718,6 @@
       </c>
       <c r="D27" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="O27" s="4" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D5C61B-CA0F-41CE-B8AF-584D7EDA1D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32612D24-5BF9-4786-A08D-98EBEBB1D13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="191">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -418,9 +418,6 @@
     <t>Развить идею логана</t>
   </si>
   <si>
-    <t>Развить идею GGD</t>
-  </si>
-  <si>
     <t>Сократить роботов с прибылью 1к1</t>
   </si>
   <si>
@@ -587,6 +584,30 @@
   </si>
   <si>
     <t>Добавить группы параметров к эвол. Моделям</t>
+  </si>
+  <si>
+    <t>Развить идею GGD, канал дельт фракталов</t>
+  </si>
+  <si>
+    <t>Среднее расстояние между фракталами (адаптивных канал)</t>
+  </si>
+  <si>
+    <t>Изучить skew и kurt</t>
+  </si>
+  <si>
+    <t>LTA_BIBI</t>
+  </si>
+  <si>
+    <t>LTA_IGOGOSHA</t>
+  </si>
+  <si>
+    <t>LTA_IRONANNY</t>
+  </si>
+  <si>
+    <t>PTA4_U3</t>
+  </si>
+  <si>
+    <t>Вывод графиков с fee при оптимизации</t>
   </si>
 </sst>
 </file>
@@ -602,7 +623,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -639,12 +660,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -658,7 +673,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -692,9 +707,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1091,13 +1103,13 @@
         <v>54</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="P2" s="12" t="s">
-        <v>174</v>
+        <v>164</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>5</v>
@@ -1132,13 +1144,13 @@
         <v>116</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>107</v>
@@ -1173,10 +1185,10 @@
         <v>123</v>
       </c>
       <c r="P4" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>106</v>
@@ -1205,19 +1217,19 @@
         <v>115</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>51</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1243,19 +1255,19 @@
         <v>110</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>76</v>
       </c>
       <c r="S6" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1281,19 +1293,19 @@
         <v>117</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1316,10 +1328,13 @@
         <v>118</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>70</v>
@@ -1348,19 +1363,22 @@
         <v>119</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S9" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1380,13 +1398,16 @@
         <v>122</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="S10" s="2" t="s">
         <v>38</v>
@@ -1412,19 +1433,22 @@
         <v>124</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="90" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1444,13 +1468,16 @@
         <v>125</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>78</v>
@@ -1476,16 +1503,19 @@
         <v>121</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1505,16 +1535,16 @@
         <v>89</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="R14" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1534,16 +1564,19 @@
         <v>90</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1557,16 +1590,16 @@
         <v>92</v>
       </c>
       <c r="O16" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q16" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="P16" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1580,16 +1613,13 @@
         <v>93</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1603,13 +1633,13 @@
         <v>94</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1623,13 +1653,13 @@
         <v>95</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1642,11 +1672,11 @@
       <c r="E20" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="Q20" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P20" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1656,8 +1686,11 @@
       <c r="E21" s="4" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P21" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1668,7 +1701,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1679,7 +1712,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1690,7 +1723,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1701,7 +1734,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1712,7 +1745,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1720,7 +1753,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1728,7 +1761,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1736,7 +1769,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1744,7 +1777,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1752,7 +1785,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1876,7 +1909,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B1" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="90" x14ac:dyDescent="0.25">
@@ -1884,10 +1917,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>150</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32612D24-5BF9-4786-A08D-98EBEBB1D13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0EDA0A-63E9-4143-BDA3-95EED4EE7609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="193">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -430,9 +430,6 @@
     <t>Робот на percent_zigzag</t>
   </si>
   <si>
-    <t>Робот по 4 точкам зигзага (выбрасываем последнюю)</t>
-  </si>
-  <si>
     <t>Канал допуска относительно удаленности от СС</t>
   </si>
   <si>
@@ -608,6 +605,15 @@
   </si>
   <si>
     <t>Вывод графиков с fee при оптимизации</t>
+  </si>
+  <si>
+    <t>Робот с паттернами VSA</t>
+  </si>
+  <si>
+    <t>Новый тестер стратегий</t>
+  </si>
+  <si>
+    <t>Среднедневная прибыль для analys_dbs</t>
   </si>
 </sst>
 </file>
@@ -1103,13 +1109,13 @@
         <v>54</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>5</v>
@@ -1144,13 +1150,13 @@
         <v>116</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>107</v>
@@ -1185,10 +1191,10 @@
         <v>123</v>
       </c>
       <c r="P4" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>106</v>
@@ -1217,10 +1223,10 @@
         <v>115</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>139</v>
@@ -1229,7 +1235,7 @@
         <v>51</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1255,13 +1261,13 @@
         <v>110</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>76</v>
@@ -1293,10 +1299,10 @@
         <v>117</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>154</v>
@@ -1328,13 +1334,13 @@
         <v>118</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>70</v>
@@ -1343,7 +1349,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1363,13 +1369,13 @@
         <v>119</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P9" s="4" t="s">
         <v>120</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>129</v>
@@ -1378,7 +1384,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="90" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1398,16 +1404,16 @@
         <v>122</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>138</v>
+        <v>160</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S10" s="2" t="s">
         <v>38</v>
@@ -1433,22 +1439,22 @@
         <v>124</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1468,16 +1474,16 @@
         <v>125</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>136</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>78</v>
@@ -1503,19 +1509,19 @@
         <v>121</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1535,19 +1541,22 @@
         <v>89</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="R14" s="9" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1564,19 +1573,22 @@
         <v>90</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>192</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1590,13 +1602,13 @@
         <v>92</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -1613,10 +1625,10 @@
         <v>93</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1633,10 +1645,10 @@
         <v>94</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -1653,10 +1665,10 @@
         <v>95</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -1673,7 +1685,7 @@
         <v>96</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -1687,7 +1699,7 @@
         <v>97</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -1909,7 +1921,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B1" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="90" x14ac:dyDescent="0.25">
@@ -1917,10 +1929,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0EDA0A-63E9-4143-BDA3-95EED4EE7609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D486E87-B78E-4C67-A7FC-CE16A61F3C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="195">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -614,6 +614,12 @@
   </si>
   <si>
     <t>Среднедневная прибыль для analys_dbs</t>
+  </si>
+  <si>
+    <t>PTA21_WHITEMANE</t>
+  </si>
+  <si>
+    <t>LTA версия PTA21 (без 'DC')</t>
   </si>
 </sst>
 </file>
@@ -1442,7 +1448,7 @@
         <v>166</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>135</v>
@@ -1454,7 +1460,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1475,9 +1481,6 @@
       </c>
       <c r="O12" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>136</v>
@@ -1511,9 +1514,6 @@
       <c r="O13" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="Q13" s="2" t="s">
         <v>126</v>
       </c>
@@ -1546,14 +1546,14 @@
       <c r="O14" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="Q14" s="2" t="s">
         <v>165</v>
       </c>
       <c r="R14" s="9" t="s">
         <v>176</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1587,8 +1587,11 @@
       <c r="R15" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="S15" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1610,8 +1613,11 @@
       <c r="R16" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="S16" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1630,8 +1636,11 @@
       <c r="P17" s="7" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S17" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1651,7 +1660,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1671,7 +1680,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1688,7 +1697,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1702,7 +1711,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1712,8 +1721,11 @@
       <c r="E22" s="7" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P22" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1724,7 +1736,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1735,7 +1747,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1746,7 +1758,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1757,7 +1769,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1765,7 +1777,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1773,7 +1785,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1781,7 +1793,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1789,7 +1801,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1797,7 +1809,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D486E87-B78E-4C67-A7FC-CE16A61F3C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4914B3-1DE0-4C9D-95CB-88E572E49737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="196">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -532,9 +532,6 @@
     <t>Дописать новые батники</t>
   </si>
   <si>
-    <t>Робот с фильтрацией направления по ZZ</t>
-  </si>
-  <si>
     <t>ST1 на PZZ</t>
   </si>
   <si>
@@ -619,7 +616,13 @@
     <t>PTA21_WHITEMANE</t>
   </si>
   <si>
-    <t>LTA версия PTA21 (без 'DC')</t>
+    <t>Исправить days в analys_dbs</t>
+  </si>
+  <si>
+    <t>PTA21_AURIEL</t>
+  </si>
+  <si>
+    <t>Среднее расстояние от фракталов до SMA. Таким образом можно построить канал</t>
   </si>
 </sst>
 </file>
@@ -635,7 +638,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -672,6 +675,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -685,7 +694,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -719,6 +728,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1118,7 +1130,7 @@
         <v>163</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>162</v>
@@ -1159,7 +1171,7 @@
         <v>164</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>152</v>
@@ -1196,8 +1208,8 @@
       <c r="O4" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="P4" s="9" t="s">
-        <v>173</v>
+      <c r="P4" s="4" t="s">
+        <v>193</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>138</v>
@@ -1209,7 +1221,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1231,8 +1243,8 @@
       <c r="O5" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="P5" s="2" t="s">
-        <v>178</v>
+      <c r="P5" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>139</v>
@@ -1244,7 +1256,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1270,7 +1282,7 @@
         <v>151</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>153</v>
@@ -1307,8 +1319,8 @@
       <c r="O7" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>181</v>
+      <c r="P7" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>154</v>
@@ -1320,7 +1332,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1340,10 +1352,10 @@
         <v>118</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>156</v>
@@ -1378,7 +1390,7 @@
         <v>159</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>142</v>
@@ -1390,7 +1402,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1412,8 +1424,8 @@
       <c r="O10" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="P10" s="4" t="s">
-        <v>137</v>
+      <c r="P10" s="12" t="s">
+        <v>195</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>130</v>
@@ -1445,10 +1457,7 @@
         <v>124</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>135</v>
@@ -1480,7 +1489,7 @@
         <v>125</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>136</v>
@@ -1511,8 +1520,11 @@
       <c r="L13" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="O13" s="7" t="s">
-        <v>144</v>
+      <c r="O13" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>126</v>
@@ -1521,7 +1533,7 @@
         <v>134</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1544,13 +1556,13 @@
         <v>145</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>165</v>
+        <v>144</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="R14" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>161</v>
@@ -1576,19 +1588,16 @@
         <v>146</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1604,17 +1613,17 @@
       <c r="E16" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="O16" s="4" t="s">
-        <v>167</v>
+      <c r="O16" s="7" t="s">
+        <v>158</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -1630,14 +1639,14 @@
       <c r="E17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="O17" s="7" t="s">
-        <v>170</v>
+      <c r="O17" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -1654,10 +1663,10 @@
         <v>94</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -1673,11 +1682,11 @@
       <c r="E19" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="O19" s="4" t="s">
-        <v>175</v>
+      <c r="O19" s="7" t="s">
+        <v>170</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -1693,8 +1702,11 @@
       <c r="E20" s="7" t="s">
         <v>96</v>
       </c>
+      <c r="O20" s="4" t="s">
+        <v>174</v>
+      </c>
       <c r="P20" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
@@ -1708,7 +1720,7 @@
         <v>97</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
@@ -1722,7 +1734,7 @@
         <v>98</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
@@ -1734,6 +1746,9 @@
       </c>
       <c r="E23" s="7" t="s">
         <v>99</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4914B3-1DE0-4C9D-95CB-88E572E49737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2013C0C6-1489-486D-A166-4C24B238A741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="197">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -623,6 +623,9 @@
   </si>
   <si>
     <t>Среднее расстояние от фракталов до SMA. Таким образом можно построить канал</t>
+  </si>
+  <si>
+    <t>Улучшить wizard</t>
   </si>
 </sst>
 </file>
@@ -1561,6 +1564,9 @@
       <c r="P14" s="2" t="s">
         <v>177</v>
       </c>
+      <c r="Q14" s="2" t="s">
+        <v>196</v>
+      </c>
       <c r="R14" s="9" t="s">
         <v>175</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2013C0C6-1489-486D-A166-4C24B238A741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA783EBA-3B8A-4E33-B44A-E5FD3D36EE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="202">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -622,10 +622,25 @@
     <t>PTA21_AURIEL</t>
   </si>
   <si>
-    <t>Среднее расстояние от фракталов до SMA. Таким образом можно построить канал</t>
-  </si>
-  <si>
     <t>Улучшить wizard</t>
+  </si>
+  <si>
+    <t>Идеи для инструментов с узкими боковиками</t>
+  </si>
+  <si>
+    <t>Тестирование на wss для инструметов вне ticker_group</t>
+  </si>
+  <si>
+    <t>Добавить фьючерсы на тест</t>
+  </si>
+  <si>
+    <t>Среднее расстояние от фракталов и peaks до SMA. Таким образом можно построить канал</t>
+  </si>
+  <si>
+    <t>vsai</t>
+  </si>
+  <si>
+    <t>Превышение прогнозируемого объема</t>
   </si>
 </sst>
 </file>
@@ -1428,7 +1443,7 @@
         <v>160</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>130</v>
@@ -1462,6 +1477,9 @@
       <c r="O11" s="4" t="s">
         <v>167</v>
       </c>
+      <c r="P11" s="4" t="s">
+        <v>198</v>
+      </c>
       <c r="Q11" s="2" t="s">
         <v>135</v>
       </c>
@@ -1565,7 +1583,7 @@
         <v>177</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R14" s="9" t="s">
         <v>175</v>
@@ -1599,6 +1617,9 @@
       <c r="P15" s="4" t="s">
         <v>191</v>
       </c>
+      <c r="Q15" s="2" t="s">
+        <v>196</v>
+      </c>
       <c r="R15" s="2" t="s">
         <v>183</v>
       </c>
@@ -1625,6 +1646,9 @@
       <c r="P16" s="4" t="s">
         <v>178</v>
       </c>
+      <c r="Q16" s="2" t="s">
+        <v>200</v>
+      </c>
       <c r="R16" s="2" t="s">
         <v>189</v>
       </c>
@@ -1632,7 +1656,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1650,6 +1674,12 @@
       </c>
       <c r="P17" s="7" t="s">
         <v>179</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>190</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA783EBA-3B8A-4E33-B44A-E5FD3D36EE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952775D3-3AD3-42BC-93C0-9EA3B73419E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952775D3-3AD3-42BC-93C0-9EA3B73419E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC7F643-5D0F-47F7-BAAC-3DBDFCCD7438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="203">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -641,6 +641,9 @@
   </si>
   <si>
     <t>Превышение прогнозируемого объема</t>
+  </si>
+  <si>
+    <t>Разобраться с расчетом комиссий</t>
   </si>
 </sst>
 </file>
@@ -1420,7 +1423,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1441,9 +1444,6 @@
       </c>
       <c r="O10" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="P10" s="12" t="s">
-        <v>199</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>130</v>
@@ -1512,6 +1512,9 @@
       <c r="O12" s="4" t="s">
         <v>165</v>
       </c>
+      <c r="P12" s="4" t="s">
+        <v>191</v>
+      </c>
       <c r="Q12" s="2" t="s">
         <v>136</v>
       </c>
@@ -1544,8 +1547,8 @@
       <c r="O13" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>180</v>
+      <c r="P13" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>126</v>
@@ -1579,8 +1582,8 @@
       <c r="O14" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>177</v>
+      <c r="P14" s="7" t="s">
+        <v>179</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>195</v>
@@ -1615,7 +1618,7 @@
         <v>157</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>196</v>
@@ -1643,8 +1646,8 @@
       <c r="O16" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="P16" s="4" t="s">
-        <v>178</v>
+      <c r="P16" s="7" t="s">
+        <v>185</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>200</v>
@@ -1673,7 +1676,7 @@
         <v>166</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>201</v>
@@ -1685,7 +1688,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1701,11 +1704,14 @@
       <c r="O18" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="P18" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P18" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1721,11 +1727,14 @@
       <c r="O19" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="P19" s="7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P19" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1742,10 +1751,13 @@
         <v>174</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+      <c r="Q20" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1755,8 +1767,8 @@
       <c r="E21" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="P21" s="7" t="s">
-        <v>187</v>
+      <c r="Q21" s="12" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
@@ -1769,9 +1781,6 @@
       <c r="E22" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="P22" s="4" t="s">
-        <v>192</v>
-      </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -1782,9 +1791,6 @@
       </c>
       <c r="E23" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="P23" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC7F643-5D0F-47F7-BAAC-3DBDFCCD7438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6205961-389B-49EE-9555-B2C54C4056CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="206">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -644,6 +644,15 @@
   </si>
   <si>
     <t>Разобраться с расчетом комиссий</t>
+  </si>
+  <si>
+    <t>Evolutionis2</t>
+  </si>
+  <si>
+    <t>QLearning1</t>
+  </si>
+  <si>
+    <t>Optuna Optimizator</t>
   </si>
 </sst>
 </file>
@@ -1153,8 +1162,8 @@
       <c r="P2" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>162</v>
+      <c r="Q2" s="4" t="s">
+        <v>202</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>5</v>
@@ -1162,8 +1171,11 @@
       <c r="S2" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+      <c r="T2" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1194,14 +1206,17 @@
       <c r="P3" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>152</v>
+      <c r="Q3" s="12" t="s">
+        <v>199</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>107</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>46</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1232,14 +1247,14 @@
       <c r="P4" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="R4" s="2" t="s">
         <v>106</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>47</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1267,14 +1282,14 @@
       <c r="P5" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="Q5" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="R5" s="2" t="s">
         <v>51</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>141</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1305,14 +1320,14 @@
       <c r="P6" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="Q6" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="R6" s="2" t="s">
         <v>76</v>
       </c>
       <c r="S6" s="9" t="s">
         <v>127</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1343,14 +1358,14 @@
       <c r="P7" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>128</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1378,14 +1393,14 @@
       <c r="P8" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="Q8" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="R8" s="2" t="s">
         <v>70</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>43</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="90" x14ac:dyDescent="0.25">
@@ -1413,14 +1428,14 @@
       <c r="P9" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="Q9" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="R9" s="2" t="s">
         <v>129</v>
       </c>
       <c r="S9" s="2" t="s">
         <v>45</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1445,14 +1460,17 @@
       <c r="O10" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="Q10" s="2" t="s">
-        <v>130</v>
+      <c r="P10" s="4" t="s">
+        <v>198</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>131</v>
       </c>
       <c r="S10" s="2" t="s">
         <v>38</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1478,16 +1496,16 @@
         <v>167</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>132</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>34</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1513,16 +1531,16 @@
         <v>165</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>133</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>78</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1548,16 +1566,16 @@
         <v>143</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>126</v>
+        <v>203</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>134</v>
       </c>
       <c r="S13" s="9" t="s">
         <v>168</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1582,17 +1600,17 @@
       <c r="O14" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="P14" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>195</v>
+      <c r="P14" s="4" t="s">
+        <v>205</v>
       </c>
       <c r="R14" s="9" t="s">
         <v>175</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>161</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1618,16 +1636,16 @@
         <v>157</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>183</v>
       </c>
       <c r="S15" s="2" t="s">
         <v>182</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1647,10 +1665,7 @@
         <v>158</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="R16" s="2" t="s">
         <v>189</v>
@@ -1658,8 +1673,11 @@
       <c r="S16" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="T16" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1675,11 +1693,8 @@
       <c r="O17" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="P17" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>201</v>
+      <c r="P17" s="4" t="s">
+        <v>184</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>197</v>
@@ -1687,8 +1702,11 @@
       <c r="S17" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="T17" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1705,13 +1723,13 @@
         <v>169</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q18" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="T18" s="2" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1727,14 +1745,14 @@
       <c r="O19" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="P19" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q19" s="2" t="s">
+      <c r="P19" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="T19" s="2" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1751,13 +1769,10 @@
         <v>174</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q20" s="12" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1767,11 +1782,11 @@
       <c r="E21" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="Q21" s="12" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P21" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1781,8 +1796,11 @@
       <c r="E22" s="7" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="P22" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1793,7 +1811,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1804,7 +1822,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1815,7 +1833,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1826,7 +1844,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1834,7 +1852,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1842,7 +1860,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1850,7 +1868,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1858,7 +1876,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1866,7 +1884,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6205961-389B-49EE-9555-B2C54C4056CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DBB9D9-946D-4028-B329-6E3E59E84B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="209">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -175,12 +175,6 @@
     <t>Изучить возможность оптимизации подключения к QUIK</t>
   </si>
   <si>
-    <t>Войти в топ-100 Акции</t>
-  </si>
-  <si>
-    <t>Войти в топ-100 Фьючи</t>
-  </si>
-  <si>
     <t>Индикатор по типу индексового RMI</t>
   </si>
   <si>
@@ -247,9 +241,6 @@
     <t>аппроксимация индикаторов</t>
   </si>
   <si>
-    <t>Индикатор свободы</t>
-  </si>
-  <si>
     <t>PTA18_REXXAR</t>
   </si>
   <si>
@@ -653,6 +644,24 @@
   </si>
   <si>
     <t>Optuna Optimizator</t>
+  </si>
+  <si>
+    <t>Поправить пики king</t>
+  </si>
+  <si>
+    <t>Динамический выбор файлов с пиками king. Ожидаем рост лонговые стратегии и т.д.</t>
+  </si>
+  <si>
+    <t>Робот по анализу dzz (можно GLTA)</t>
+  </si>
+  <si>
+    <t>Почистить wss</t>
+  </si>
+  <si>
+    <t>Провести оптимизацию лучших роботов</t>
+  </si>
+  <si>
+    <t>Провести оптимизацию роботов для Bitget</t>
   </si>
 </sst>
 </file>
@@ -668,7 +677,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -705,12 +714,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -724,7 +727,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -758,9 +761,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1139,31 +1139,31 @@
         <v>41</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="L2" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>5</v>
@@ -1172,7 +1172,7 @@
         <v>36</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1189,34 +1189,34 @@
         <v>42</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q3" s="12" t="s">
-        <v>199</v>
+        <v>173</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>46</v>
+        <v>138</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1233,28 +1233,28 @@
         <v>30</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>138</v>
+        <v>103</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1271,25 +1271,28 @@
         <v>32</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1306,28 +1309,31 @@
         <v>33</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="S6" s="9" t="s">
-        <v>127</v>
+        <v>73</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1344,31 +1350,34 @@
         <v>37</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L7" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="P7" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="O7" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>120</v>
+      <c r="Q7" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1382,28 +1391,31 @@
         <v>40</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="90" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1414,31 +1426,34 @@
         <v>3</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>159</v>
+        <v>116</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>156</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1449,31 +1464,34 @@
         <v>21</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>205</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1484,31 +1502,31 @@
         <v>24</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1519,31 +1537,34 @@
         <v>25</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="O12" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="P12" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="P12" s="4" t="s">
-        <v>204</v>
+      <c r="Q12" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1554,31 +1575,31 @@
         <v>26</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="S13" s="9" t="s">
-        <v>168</v>
+        <v>201</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>172</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1589,31 +1610,25 @@
         <v>27</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="R14" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1624,31 +1639,28 @@
         <v>28</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1656,25 +1668,22 @@
         <v>15</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="P16" s="7" t="s">
-        <v>179</v>
+        <v>155</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>185</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="45" x14ac:dyDescent="0.25">
@@ -1685,28 +1694,25 @@
         <v>16</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1717,19 +1723,16 @@
         <v>39</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="P18" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1737,19 +1740,16 @@
         <v>18</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -1760,16 +1760,16 @@
         <v>19</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="P20" s="7" t="s">
-        <v>187</v>
+        <v>171</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -1777,13 +1777,13 @@
         <v>20</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="P21" s="4" t="s">
-        <v>192</v>
+        <v>94</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -1791,13 +1791,13 @@
         <v>21</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -1805,10 +1805,13 @@
         <v>22</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -1816,10 +1819,13 @@
         <v>23</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -1827,10 +1833,13 @@
         <v>24</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -1838,10 +1847,10 @@
         <v>25</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -1849,7 +1858,7 @@
         <v>26</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -1857,7 +1866,7 @@
         <v>27</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -1865,7 +1874,7 @@
         <v>28</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -1873,7 +1882,7 @@
         <v>29</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -1881,7 +1890,7 @@
         <v>30</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -1889,7 +1898,7 @@
         <v>31</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1897,7 +1906,7 @@
         <v>32</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2008,7 +2017,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B1" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="90" x14ac:dyDescent="0.25">
@@ -2016,10 +2025,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DBB9D9-946D-4028-B329-6E3E59E84B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86DB371-C412-4781-BFCD-A8ED2F5B7CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="212">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -662,6 +662,15 @@
   </si>
   <si>
     <t>Провести оптимизацию роботов для Bitget</t>
+  </si>
+  <si>
+    <t>Valeera + LTA2</t>
+  </si>
+  <si>
+    <t>Valeera со входом за пределом BB</t>
+  </si>
+  <si>
+    <t>Проблемы с Оптуной</t>
   </si>
 </sst>
 </file>
@@ -677,7 +686,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -714,6 +723,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -727,7 +742,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -761,6 +776,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1624,6 +1642,9 @@
       <c r="P14" s="4" t="s">
         <v>200</v>
       </c>
+      <c r="Q14" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="T14" s="2" t="s">
         <v>197</v>
       </c>
@@ -1653,6 +1674,9 @@
       <c r="P15" s="4" t="s">
         <v>202</v>
       </c>
+      <c r="Q15" s="2" t="s">
+        <v>210</v>
+      </c>
       <c r="R15" s="2" t="s">
         <v>180</v>
       </c>
@@ -1678,6 +1702,9 @@
       </c>
       <c r="P16" s="4" t="s">
         <v>185</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>211</v>
       </c>
       <c r="R16" s="2" t="s">
         <v>186</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86DB371-C412-4781-BFCD-A8ED2F5B7CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA505568-DA06-4F96-AD2D-6B41131B0519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="213">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -671,6 +671,9 @@
   </si>
   <si>
     <t>Проблемы с Оптуной</t>
+  </si>
+  <si>
+    <t>Добавить в чек просадки и абсолютный тотал - фии</t>
   </si>
 </sst>
 </file>
@@ -1265,7 +1268,7 @@
       <c r="P4" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="Q4" s="4" t="s">
         <v>203</v>
       </c>
       <c r="R4" s="2" t="s">
@@ -1300,8 +1303,8 @@
       <c r="P5" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="Q5" s="2" t="s">
-        <v>192</v>
+      <c r="Q5" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>49</v>
@@ -1309,8 +1312,8 @@
       <c r="S5" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="T5" s="2" t="s">
-        <v>136</v>
+      <c r="U5" s="2" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1341,8 +1344,8 @@
       <c r="P6" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="Q6" s="2" t="s">
-        <v>135</v>
+      <c r="Q6" s="4" t="s">
+        <v>211</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>73</v>
@@ -1352,6 +1355,9 @@
       </c>
       <c r="T6" s="2" t="s">
         <v>150</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1382,8 +1388,8 @@
       <c r="P7" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>158</v>
+      <c r="Q7" s="12" t="s">
+        <v>212</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>67</v>
@@ -1393,6 +1399,9 @@
       </c>
       <c r="T7" s="2" t="s">
         <v>151</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="90" x14ac:dyDescent="0.25">
@@ -1421,7 +1430,7 @@
         <v>134</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>126</v>
@@ -1431,6 +1440,9 @@
       </c>
       <c r="T8" s="2" t="s">
         <v>153</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1458,9 +1470,6 @@
       <c r="P9" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="Q9" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="R9" s="2" t="s">
         <v>128</v>
       </c>
@@ -1469,6 +1478,9 @@
       </c>
       <c r="T9" s="2" t="s">
         <v>127</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1496,9 +1508,6 @@
       <c r="P10" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="Q10" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="R10" s="2" t="s">
         <v>129</v>
       </c>
@@ -1507,6 +1516,9 @@
       </c>
       <c r="T10" s="2" t="s">
         <v>132</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1534,14 +1546,14 @@
       <c r="P11" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="Q11" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="R11" s="2" t="s">
         <v>130</v>
       </c>
       <c r="T11" s="2" t="s">
         <v>133</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1569,9 +1581,6 @@
       <c r="P12" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="Q12" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="R12" s="2" t="s">
         <v>131</v>
       </c>
@@ -1580,6 +1589,9 @@
       </c>
       <c r="T12" s="2" t="s">
         <v>123</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1607,17 +1619,17 @@
       <c r="P13" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="Q13" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="R13" s="9" t="s">
         <v>172</v>
       </c>
+      <c r="S13" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="T13" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1642,8 +1654,8 @@
       <c r="P14" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="Q14" s="2" t="s">
-        <v>209</v>
+      <c r="S14" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="T14" s="2" t="s">
         <v>197</v>
@@ -1674,9 +1686,6 @@
       <c r="P15" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="Q15" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="R15" s="2" t="s">
         <v>180</v>
       </c>
@@ -1702,9 +1711,6 @@
       </c>
       <c r="P16" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="Q16" s="12" t="s">
-        <v>211</v>
       </c>
       <c r="R16" s="2" t="s">
         <v>186</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA505568-DA06-4F96-AD2D-6B41131B0519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492BFB2F-B0AF-4C93-80DB-2EB6F28FC893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="214">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -674,6 +674,9 @@
   </si>
   <si>
     <t>Добавить в чек просадки и абсолютный тотал - фии</t>
+  </si>
+  <si>
+    <t>Разобраться с ошибкой в VT</t>
   </si>
 </sst>
 </file>
@@ -689,7 +692,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -726,12 +729,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -745,7 +742,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -779,9 +776,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1388,7 +1382,7 @@
       <c r="P7" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="Q7" s="12" t="s">
+      <c r="Q7" s="4" t="s">
         <v>212</v>
       </c>
       <c r="R7" s="2" t="s">
@@ -1430,7 +1424,7 @@
         <v>134</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>136</v>
+        <v>213</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>126</v>
@@ -1469,6 +1463,9 @@
       </c>
       <c r="P9" s="4" t="s">
         <v>169</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>128</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492BFB2F-B0AF-4C93-80DB-2EB6F28FC893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A7A1EF-7034-4808-8410-DBC079CD1D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="216">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -445,9 +445,6 @@
     <t>Фибо по зигзагу</t>
   </si>
   <si>
-    <t>Тиковый тестер</t>
-  </si>
-  <si>
     <t>pta14_ranger (определять боковик по большому adx)</t>
   </si>
   <si>
@@ -677,6 +674,15 @@
   </si>
   <si>
     <t>Разобраться с ошибкой в VT</t>
+  </si>
+  <si>
+    <t>Шаговый тестер</t>
+  </si>
+  <si>
+    <t>Протестировать все wss на шаговом тестере</t>
+  </si>
+  <si>
+    <t>PTA22_BERSERK</t>
   </si>
 </sst>
 </file>
@@ -692,7 +698,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -729,6 +735,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -742,7 +754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -776,6 +788,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1172,13 +1187,13 @@
         <v>52</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>5</v>
@@ -1187,7 +1202,7 @@
         <v>36</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1216,22 +1231,22 @@
         <v>113</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>104</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1260,10 +1275,10 @@
         <v>120</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>103</v>
@@ -1292,13 +1307,13 @@
         <v>112</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>49</v>
@@ -1307,7 +1322,7 @@
         <v>125</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1333,13 +1348,13 @@
         <v>107</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>73</v>
@@ -1348,7 +1363,7 @@
         <v>43</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="U6" s="2" t="s">
         <v>135</v>
@@ -1377,13 +1392,13 @@
         <v>114</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P7" s="4" t="s">
         <v>117</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>67</v>
@@ -1392,10 +1407,10 @@
         <v>45</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="90" x14ac:dyDescent="0.25">
@@ -1418,13 +1433,13 @@
         <v>115</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P8" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="Q8" s="2" t="s">
-        <v>213</v>
+      <c r="Q8" s="4" t="s">
+        <v>212</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>126</v>
@@ -1433,10 +1448,10 @@
         <v>38</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1459,13 +1474,13 @@
         <v>116</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>136</v>
+        <v>168</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>128</v>
@@ -1477,7 +1492,7 @@
         <v>127</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1500,10 +1515,13 @@
         <v>119</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>214</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>129</v>
@@ -1515,7 +1533,7 @@
         <v>132</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1538,10 +1556,10 @@
         <v>121</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>130</v>
@@ -1550,7 +1568,7 @@
         <v>133</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1573,22 +1591,22 @@
         <v>122</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>131</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="T12" s="2" t="s">
         <v>123</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1611,19 +1629,19 @@
         <v>118</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R13" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1643,19 +1661,19 @@
         <v>86</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1675,19 +1693,19 @@
         <v>87</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1704,16 +1722,16 @@
         <v>89</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P16" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="R16" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="R16" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="T16" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="45" x14ac:dyDescent="0.25">
@@ -1730,16 +1748,16 @@
         <v>90</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -1756,10 +1774,13 @@
         <v>91</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -1776,10 +1797,10 @@
         <v>92</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -1796,10 +1817,10 @@
         <v>93</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -1813,7 +1834,7 @@
         <v>94</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -1827,7 +1848,7 @@
         <v>95</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -1841,7 +1862,7 @@
         <v>96</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -1855,7 +1876,7 @@
         <v>97</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -1869,7 +1890,7 @@
         <v>98</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -2047,7 +2068,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B1" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="90" x14ac:dyDescent="0.25">
@@ -2055,10 +2076,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A7A1EF-7034-4808-8410-DBC079CD1D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FF350B-047F-447A-84DA-D790C208F543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="220">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -683,6 +683,18 @@
   </si>
   <si>
     <t>PTA22_BERSERK</t>
+  </si>
+  <si>
+    <t>LOGAN + LTA2</t>
+  </si>
+  <si>
+    <t>LOGAN + PTA21</t>
+  </si>
+  <si>
+    <t>DDCrVG + PTA21 or LTA2</t>
+  </si>
+  <si>
+    <t>Рангер без стопа</t>
   </si>
 </sst>
 </file>
@@ -698,7 +710,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -735,12 +747,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -754,7 +760,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -788,9 +794,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1520,7 +1523,7 @@
       <c r="P10" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="Q10" s="12" t="s">
+      <c r="Q10" s="4" t="s">
         <v>214</v>
       </c>
       <c r="R10" s="2" t="s">
@@ -1561,6 +1564,9 @@
       <c r="P11" s="4" t="s">
         <v>187</v>
       </c>
+      <c r="Q11" s="2" t="s">
+        <v>219</v>
+      </c>
       <c r="R11" s="2" t="s">
         <v>130</v>
       </c>
@@ -1704,6 +1710,9 @@
       <c r="R15" s="2" t="s">
         <v>179</v>
       </c>
+      <c r="S15" s="2" t="s">
+        <v>216</v>
+      </c>
       <c r="T15" s="2" t="s">
         <v>197</v>
       </c>
@@ -1730,6 +1739,9 @@
       <c r="R16" s="2" t="s">
         <v>185</v>
       </c>
+      <c r="S16" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="T16" s="2" t="s">
         <v>176</v>
       </c>
@@ -1755,6 +1767,9 @@
       </c>
       <c r="R17" s="2" t="s">
         <v>193</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>218</v>
       </c>
       <c r="T17" s="2" t="s">
         <v>173</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FF350B-047F-447A-84DA-D790C208F543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF03999E-A0E0-4BA3-95B9-05D687122452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="210">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -139,9 +139,6 @@
     <t>оптимизировать комиссию роботов акций мосбиржи</t>
   </si>
   <si>
-    <t>Добавить выбор лучшего таймфрейма</t>
-  </si>
-  <si>
     <t>Добавить дату первой сделки</t>
   </si>
   <si>
@@ -151,9 +148,6 @@
     <t>FractalChannel</t>
   </si>
   <si>
-    <t>добавить Other другим MTA</t>
-  </si>
-  <si>
     <t>PTA15_SILVANA</t>
   </si>
   <si>
@@ -172,9 +166,6 @@
     <t>Добавить тайм-менеджмент в QT</t>
   </si>
   <si>
-    <t>Изучить возможность оптимизации подключения к QUIK</t>
-  </si>
-  <si>
     <t>Индикатор по типу индексового RMI</t>
   </si>
   <si>
@@ -184,9 +175,6 @@
     <t>STAML2_GOLDENMEAN</t>
   </si>
   <si>
-    <t>picks_GAMBIT</t>
-  </si>
-  <si>
     <t>Добавить инфо о выбранных стратегиях в кинг</t>
   </si>
   <si>
@@ -262,9 +250,6 @@
     <t>Провести оптимизацию под минутки</t>
   </si>
   <si>
-    <t xml:space="preserve">Надо что-то делать с оценкой текущей позиции. </t>
-  </si>
-  <si>
     <t>Индикатор CASCADE</t>
   </si>
   <si>
@@ -346,9 +331,6 @@
     <t>добавить перестраховку закрытия лишних позиций в QT</t>
   </si>
   <si>
-    <t>Исправленная версия stairs</t>
-  </si>
-  <si>
     <t>Алгоритм обределения боковика (диапазона)</t>
   </si>
   <si>
@@ -409,9 +391,6 @@
     <t>Развить идею логана</t>
   </si>
   <si>
-    <t>Сократить роботов с прибылью 1к1</t>
-  </si>
-  <si>
     <t>Разобраться с проблемами P2P</t>
   </si>
   <si>
@@ -430,9 +409,6 @@
     <t>Написать индикаторы придуманные дипсик</t>
   </si>
   <si>
-    <t>Добавить взвешенную дельту сердних просадок и прибыли в анализ</t>
-  </si>
-  <si>
     <t xml:space="preserve">Робот по оцениванию объемов (куммулятивной дельты) в определенных местах. </t>
   </si>
   <si>
@@ -556,18 +532,12 @@
     <t>Пересмотреть политику закрытия сделок VT в 18:26</t>
   </si>
   <si>
-    <t>Сделать разные критерии оценки Эвол. Моделей</t>
-  </si>
-  <si>
     <t>PTA20_HANZO</t>
   </si>
   <si>
     <t>PTA20_HOGGER</t>
   </si>
   <si>
-    <t>Добавить группы параметров к эвол. Моделям</t>
-  </si>
-  <si>
     <t>Развить идею GGD, канал дельт фракталов</t>
   </si>
   <si>
@@ -655,9 +625,6 @@
     <t>Почистить wss</t>
   </si>
   <si>
-    <t>Провести оптимизацию лучших роботов</t>
-  </si>
-  <si>
     <t>Провести оптимизацию роботов для Bitget</t>
   </si>
   <si>
@@ -694,7 +661,10 @@
     <t>DDCrVG + PTA21 or LTA2</t>
   </si>
   <si>
-    <t>Рангер без стопа</t>
+    <t>PTA14_RENEGADE</t>
+  </si>
+  <si>
+    <t>Проанализировать результаты стептеста акции</t>
   </si>
 </sst>
 </file>
@@ -1169,43 +1139,46 @@
         <v>20</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="O2" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>167</v>
-      </c>
       <c r="Q2" s="4" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>158</v>
+        <v>150</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1219,37 +1192,40 @@
         <v>22</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1266,31 +1242,37 @@
         <v>30</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="S4" s="9" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1304,31 +1286,34 @@
         <v>32</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>125</v>
+        <v>41</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1342,34 +1327,34 @@
         <v>33</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="L6" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="O6" s="4" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>43</v>
+        <v>168</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>135</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1383,40 +1368,40 @@
         <v>29</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>45</v>
+        <v>197</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="90" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1424,40 +1409,37 @@
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>38</v>
+        <v>198</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1468,34 +1450,31 @@
         <v>3</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>34</v>
+        <v>205</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>203</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1509,34 +1488,31 @@
         <v>21</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>129</v>
+        <v>203</v>
+      </c>
+      <c r="R10" s="9" t="s">
+        <v>163</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>75</v>
+        <v>206</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>204</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1550,31 +1526,31 @@
         <v>24</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>130</v>
+        <v>169</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1588,34 +1564,31 @@
         <v>25</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1626,31 +1599,28 @@
         <v>26</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="R13" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>208</v>
+        <v>190</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>209</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1661,28 +1631,22 @@
         <v>27</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1693,31 +1657,22 @@
         <v>28</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1725,28 +1680,19 @@
         <v>15</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1754,28 +1700,19 @@
         <v>16</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1783,22 +1720,22 @@
         <v>17</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="O18" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="P18" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="P18" s="4" t="s">
-        <v>174</v>
-      </c>
       <c r="Q18" s="4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1806,19 +1743,22 @@
         <v>18</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="O19" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="P19" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="P19" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q19" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1826,145 +1766,145 @@
         <v>19</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="O20" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="P20" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="P20" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1972,7 +1912,7 @@
         <v>32</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2083,7 +2023,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B1" s="10" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="90" x14ac:dyDescent="0.25">
@@ -2091,10 +2031,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF03999E-A0E0-4BA3-95B9-05D687122452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1341A82E-FD0D-485C-B592-35F529497800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="217">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -580,9 +580,6 @@
     <t>PTA21_AURIEL</t>
   </si>
   <si>
-    <t>Улучшить wizard</t>
-  </si>
-  <si>
     <t>Идеи для инструментов с узкими боковиками</t>
   </si>
   <si>
@@ -665,6 +662,30 @@
   </si>
   <si>
     <t>Проанализировать результаты стептеста акции</t>
+  </si>
+  <si>
+    <t>Сети КАН</t>
+  </si>
+  <si>
+    <t>OGTA4_HAMSTER</t>
+  </si>
+  <si>
+    <t>OGTA4_RAT</t>
+  </si>
+  <si>
+    <t>OGTA6_CERBERUS</t>
+  </si>
+  <si>
+    <t>OGTA7_PARADOX</t>
+  </si>
+  <si>
+    <t>Индикатор идеальной стратегии</t>
+  </si>
+  <si>
+    <t>PSTA3_REVAN</t>
+  </si>
+  <si>
+    <t>STAML2a_PHENOMENON</t>
   </si>
 </sst>
 </file>
@@ -1166,10 +1187,10 @@
         <v>159</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>5</v>
+        <v>187</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>185</v>
       </c>
       <c r="S2" s="2" t="s">
         <v>35</v>
@@ -1177,8 +1198,11 @@
       <c r="T2" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="U2" s="2" t="s">
-        <v>181</v>
+      <c r="U2" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1213,10 +1237,10 @@
         <v>164</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>98</v>
+        <v>184</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>214</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>129</v>
@@ -1225,10 +1249,13 @@
         <v>140</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1257,10 +1284,7 @@
         <v>179</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>69</v>
+        <v>191</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>118</v>
@@ -1269,10 +1293,13 @@
         <v>141</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" ht="90" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1298,10 +1325,7 @@
         <v>138</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>63</v>
+        <v>195</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>41</v>
@@ -1310,10 +1334,13 @@
         <v>142</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1342,10 +1369,7 @@
         <v>167</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>119</v>
+        <v>198</v>
       </c>
       <c r="S6" s="2" t="s">
         <v>168</v>
@@ -1355,6 +1379,9 @@
       </c>
       <c r="U6" s="2" t="s">
         <v>193</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1386,19 +1413,19 @@
         <v>111</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>121</v>
+        <v>199</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>120</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>194</v>
+        <v>209</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1427,16 +1454,19 @@
         <v>126</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>122</v>
+        <v>200</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>124</v>
+      </c>
+      <c r="U8" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1465,16 +1495,13 @@
         <v>160</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="R9" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="V9" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1500,19 +1527,19 @@
         <v>148</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="R10" s="9" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T10" s="2" t="s">
         <v>117</v>
+      </c>
+      <c r="V10" s="9" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1540,17 +1567,17 @@
       <c r="P11" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="Q11" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="R11" s="2" t="s">
+      <c r="Q11" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="V11" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1579,13 +1606,10 @@
         <v>156</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="R12" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="V12" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1611,13 +1635,13 @@
         <v>131</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>209</v>
+        <v>189</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
@@ -1643,7 +1667,13 @@
         <v>132</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
@@ -1669,7 +1699,13 @@
         <v>145</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1691,8 +1727,11 @@
       <c r="P16" s="4" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="R16" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1711,8 +1750,11 @@
       <c r="P17" s="4" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R17" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1731,11 +1773,11 @@
       <c r="P18" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="Q18" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R18" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1754,11 +1796,11 @@
       <c r="P19" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="Q19" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R19" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1778,7 +1820,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1792,7 +1834,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1806,7 +1848,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1820,7 +1862,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1834,7 +1876,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1848,7 +1890,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1859,7 +1901,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1867,7 +1909,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1875,7 +1917,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1883,7 +1925,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1891,7 +1933,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1899,7 +1941,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1341A82E-FD0D-485C-B592-35F529497800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B394954-CF38-49FF-8EF5-D58F506A8336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="222">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -686,6 +686,21 @@
   </si>
   <si>
     <t>STAML2a_PHENOMENON</t>
+  </si>
+  <si>
+    <t>Добавить vtb_fee к другим тестам</t>
+  </si>
+  <si>
+    <t>PTA21 оценивать не только средний тренд, сколько соотношение пиков</t>
+  </si>
+  <si>
+    <t>STAML c bool фичами</t>
+  </si>
+  <si>
+    <t>Уровень следующего пика ZZ</t>
+  </si>
+  <si>
+    <t>Что-то типа биржевик бота для акций</t>
   </si>
 </sst>
 </file>
@@ -701,7 +716,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -738,6 +753,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -751,7 +772,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -785,6 +806,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1286,6 +1310,9 @@
       <c r="Q4" s="4" t="s">
         <v>191</v>
       </c>
+      <c r="R4" s="12" t="s">
+        <v>217</v>
+      </c>
       <c r="S4" s="2" t="s">
         <v>118</v>
       </c>
@@ -1327,6 +1354,9 @@
       <c r="Q5" s="4" t="s">
         <v>195</v>
       </c>
+      <c r="R5" s="2" t="s">
+        <v>218</v>
+      </c>
       <c r="S5" s="2" t="s">
         <v>41</v>
       </c>
@@ -1371,6 +1401,9 @@
       <c r="Q6" s="4" t="s">
         <v>198</v>
       </c>
+      <c r="R6" s="2" t="s">
+        <v>219</v>
+      </c>
       <c r="S6" s="2" t="s">
         <v>168</v>
       </c>
@@ -1415,6 +1448,9 @@
       <c r="Q7" s="4" t="s">
         <v>199</v>
       </c>
+      <c r="R7" s="2" t="s">
+        <v>220</v>
+      </c>
       <c r="S7" s="2" t="s">
         <v>196</v>
       </c>
@@ -1455,6 +1491,9 @@
       </c>
       <c r="Q8" s="4" t="s">
         <v>200</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>221</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>197</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B394954-CF38-49FF-8EF5-D58F506A8336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D932491-BA24-41A1-8DBD-E5DEB6CBC1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="223">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -701,6 +701,9 @@
   </si>
   <si>
     <t>Что-то типа биржевик бота для акций</t>
+  </si>
+  <si>
+    <t>LTA_CC</t>
   </si>
 </sst>
 </file>
@@ -1858,6 +1861,9 @@
       <c r="P20" s="4" t="s">
         <v>170</v>
       </c>
+      <c r="R20" s="4" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D932491-BA24-41A1-8DBD-E5DEB6CBC1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC3110F-FBB1-460B-87B1-C352F171BD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -700,10 +700,10 @@
     <t>Уровень следующего пика ZZ</t>
   </si>
   <si>
-    <t>Что-то типа биржевик бота для акций</t>
-  </si>
-  <si>
     <t>LTA_CC</t>
+  </si>
+  <si>
+    <t>Что-то типа биржевик бота для акций (CrisisDetecor)</t>
   </si>
 </sst>
 </file>
@@ -719,7 +719,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -756,12 +756,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -775,7 +769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -809,9 +803,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1313,7 +1304,7 @@
       <c r="Q4" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="R4" s="4" t="s">
         <v>217</v>
       </c>
       <c r="S4" s="2" t="s">
@@ -1495,8 +1486,8 @@
       <c r="Q8" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="R8" s="2" t="s">
-        <v>221</v>
+      <c r="R8" s="4" t="s">
+        <v>222</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>197</v>
@@ -1862,7 +1853,7 @@
         <v>170</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC3110F-FBB1-460B-87B1-C352F171BD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9205BF16-F4DF-4688-950B-B50E3F8EFE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="230">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -704,6 +704,27 @@
   </si>
   <si>
     <t>Что-то типа биржевик бота для акций (CrisisDetecor)</t>
+  </si>
+  <si>
+    <t>Индикатор Конверт Надарая-Уотсона</t>
+  </si>
+  <si>
+    <t>Заменить тест MTA на дополнительные акции и фьючерсы</t>
+  </si>
+  <si>
+    <t>STAML2b_RAPTOR</t>
+  </si>
+  <si>
+    <t>Канал +средних дельт между фракталами. (по типу GGD)</t>
+  </si>
+  <si>
+    <t>Шаговое тестирование 5 минутки 1-минутками</t>
+  </si>
+  <si>
+    <t>СС по DC</t>
+  </si>
+  <si>
+    <t>Перевести CNY на более старший таймфрейм</t>
   </si>
 </sst>
 </file>
@@ -719,7 +740,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -756,6 +777,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -769,7 +796,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -803,6 +830,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1395,7 +1425,7 @@
       <c r="Q6" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="R6" s="4" t="s">
         <v>219</v>
       </c>
       <c r="S6" s="2" t="s">
@@ -1530,8 +1560,14 @@
       <c r="Q9" s="4" t="s">
         <v>201</v>
       </c>
+      <c r="R9" s="2" t="s">
+        <v>229</v>
+      </c>
       <c r="S9" s="2" t="s">
         <v>204</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>223</v>
       </c>
       <c r="V9" s="2" t="s">
         <v>123</v>
@@ -1565,6 +1601,9 @@
       <c r="Q10" s="4" t="s">
         <v>202</v>
       </c>
+      <c r="R10" s="12" t="s">
+        <v>224</v>
+      </c>
       <c r="S10" s="2" t="s">
         <v>205</v>
       </c>
@@ -1603,6 +1642,9 @@
       <c r="Q11" s="4" t="s">
         <v>194</v>
       </c>
+      <c r="R11" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="S11" s="2" t="s">
         <v>206</v>
       </c>
@@ -1641,6 +1683,9 @@
       <c r="Q12" s="4" t="s">
         <v>182</v>
       </c>
+      <c r="R12" s="2" t="s">
+        <v>227</v>
+      </c>
       <c r="V12" s="2" t="s">
         <v>175</v>
       </c>
@@ -1673,6 +1718,9 @@
       <c r="Q13" s="4" t="s">
         <v>208</v>
       </c>
+      <c r="R13" s="2" t="s">
+        <v>228</v>
+      </c>
       <c r="T13" s="2" t="s">
         <v>186</v>
       </c>
@@ -1868,6 +1916,9 @@
       </c>
       <c r="P21" s="7" t="s">
         <v>171</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9205BF16-F4DF-4688-950B-B50E3F8EFE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24068D69-5009-470D-BA2E-0CAD1907E519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -740,7 +740,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -777,12 +777,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -796,7 +790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -830,9 +824,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1378,8 +1369,8 @@
       <c r="Q5" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="R5" s="2" t="s">
-        <v>218</v>
+      <c r="R5" s="4" t="s">
+        <v>219</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>41</v>
@@ -1426,7 +1417,7 @@
         <v>198</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S6" s="2" t="s">
         <v>168</v>
@@ -1472,8 +1463,8 @@
       <c r="Q7" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>220</v>
+      <c r="R7" s="4" t="s">
+        <v>224</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>196</v>
@@ -1516,9 +1507,6 @@
       <c r="Q8" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="R8" s="4" t="s">
-        <v>222</v>
-      </c>
       <c r="S8" s="2" t="s">
         <v>197</v>
       </c>
@@ -1560,9 +1548,6 @@
       <c r="Q9" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="R9" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="S9" s="2" t="s">
         <v>204</v>
       </c>
@@ -1601,9 +1586,6 @@
       <c r="Q10" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="R10" s="12" t="s">
-        <v>224</v>
-      </c>
       <c r="S10" s="2" t="s">
         <v>205</v>
       </c>
@@ -1642,9 +1624,6 @@
       <c r="Q11" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="R11" s="2" t="s">
-        <v>226</v>
-      </c>
       <c r="S11" s="2" t="s">
         <v>206</v>
       </c>
@@ -1683,8 +1662,8 @@
       <c r="Q12" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="R12" s="2" t="s">
-        <v>227</v>
+      <c r="S12" s="2" t="s">
+        <v>218</v>
       </c>
       <c r="V12" s="2" t="s">
         <v>175</v>
@@ -1718,14 +1697,14 @@
       <c r="Q13" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="R13" s="2" t="s">
-        <v>228</v>
+      <c r="S13" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1756,8 +1735,11 @@
       <c r="R14" s="7" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="S14" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1787,6 +1769,9 @@
       </c>
       <c r="R15" s="7" t="s">
         <v>211</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1811,8 +1796,11 @@
       <c r="R16" s="4" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="S16" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1834,8 +1822,11 @@
       <c r="R17" s="4" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S17" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1858,7 +1849,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1881,7 +1872,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1904,7 +1895,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1921,7 +1912,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1935,7 +1926,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1949,7 +1940,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1963,7 +1954,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1977,7 +1968,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1988,7 +1979,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1996,7 +1987,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2004,7 +1995,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2012,7 +2003,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2020,7 +2011,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2028,7 +2019,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24068D69-5009-470D-BA2E-0CAD1907E519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E946B5-ED8B-4186-A8D2-573527DC12C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="239">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -725,6 +725,33 @@
   </si>
   <si>
     <t>Перевести CNY на более старший таймфрейм</t>
+  </si>
+  <si>
+    <t>Использовать kvas или kefir каналы</t>
+  </si>
+  <si>
+    <t>Добавить скрипт с информацией о pnl, текущей позиции и последних сделок на Bitget</t>
+  </si>
+  <si>
+    <t>PSTA2_GOOSE</t>
+  </si>
+  <si>
+    <t>PSTA2_DUCK</t>
+  </si>
+  <si>
+    <t>PSTA4_FALCON</t>
+  </si>
+  <si>
+    <t>PSTA4_PELICAN</t>
+  </si>
+  <si>
+    <t>PTA2_SDDCr</t>
+  </si>
+  <si>
+    <t>PTA23_ULTIMATUM</t>
+  </si>
+  <si>
+    <t>PSTA5_HAWK</t>
   </si>
 </sst>
 </file>
@@ -1232,7 +1259,7 @@
         <v>185</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>35</v>
+        <v>168</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>150</v>
@@ -1282,7 +1309,7 @@
         <v>214</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>129</v>
+        <v>196</v>
       </c>
       <c r="T3" s="2" t="s">
         <v>140</v>
@@ -1329,7 +1356,7 @@
         <v>217</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>118</v>
+        <v>197</v>
       </c>
       <c r="T4" s="2" t="s">
         <v>141</v>
@@ -1373,7 +1400,7 @@
         <v>219</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>41</v>
+        <v>204</v>
       </c>
       <c r="T5" s="2" t="s">
         <v>142</v>
@@ -1420,7 +1447,7 @@
         <v>222</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="T6" s="2" t="s">
         <v>144</v>
@@ -1467,7 +1494,7 @@
         <v>224</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>120</v>
@@ -1507,8 +1534,11 @@
       <c r="Q8" s="4" t="s">
         <v>200</v>
       </c>
+      <c r="R8" s="4" t="s">
+        <v>228</v>
+      </c>
       <c r="S8" s="2" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>124</v>
@@ -1548,11 +1578,17 @@
       <c r="Q9" s="4" t="s">
         <v>201</v>
       </c>
+      <c r="R9" s="4" t="s">
+        <v>226</v>
+      </c>
       <c r="S9" s="2" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>223</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="V9" s="2" t="s">
         <v>123</v>
@@ -1586,11 +1622,17 @@
       <c r="Q10" s="4" t="s">
         <v>202</v>
       </c>
+      <c r="R10" s="2" t="s">
+        <v>129</v>
+      </c>
       <c r="S10" s="2" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="T10" s="2" t="s">
         <v>117</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="V10" s="9" t="s">
         <v>163</v>
@@ -1625,10 +1667,13 @@
         <v>194</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="T11" s="2" t="s">
         <v>181</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="V11" s="2" t="s">
         <v>169</v>
@@ -1663,13 +1708,13 @@
         <v>182</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="V12" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1698,13 +1743,13 @@
         <v>208</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1735,11 +1780,8 @@
       <c r="R14" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="S14" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1769,9 +1811,6 @@
       </c>
       <c r="R15" s="7" t="s">
         <v>211</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1796,11 +1835,8 @@
       <c r="R16" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="S16" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1822,11 +1858,8 @@
       <c r="R17" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="S17" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1849,7 +1882,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1872,7 +1905,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1895,7 +1928,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1912,7 +1945,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1925,8 +1958,11 @@
       <c r="P22" s="7" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R22" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1939,8 +1975,11 @@
       <c r="P23" s="7" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R23" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1953,8 +1992,11 @@
       <c r="P24" s="4" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R24" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1967,8 +2009,11 @@
       <c r="P25" s="7" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R25" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1978,24 +2023,33 @@
       <c r="E26" s="7" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R26" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R27" s="4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R28" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2003,7 +2057,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2011,7 +2065,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2019,7 +2073,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E946B5-ED8B-4186-A8D2-573527DC12C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705AD1C3-DFA2-443A-BEE2-71B36E61F101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="247">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -697,9 +697,6 @@
     <t>STAML c bool фичами</t>
   </si>
   <si>
-    <t>Уровень следующего пика ZZ</t>
-  </si>
-  <si>
     <t>LTA_CC</t>
   </si>
   <si>
@@ -752,18 +749,54 @@
   </si>
   <si>
     <t>PSTA5_HAWK</t>
+  </si>
+  <si>
+    <t>Чистка дбшек по времени</t>
+  </si>
+  <si>
+    <t>Добавить время ошибки в QT</t>
+  </si>
+  <si>
+    <t>Ranger без DC, +logan, + fm_rsi, ggd (тоже самое для pta19,pta21,lta2</t>
+  </si>
+  <si>
+    <t>ggd+направление</t>
+  </si>
+  <si>
+    <t>Уровень следующего пика ZZ (как с фракталами в Goose или Duck</t>
+  </si>
+  <si>
+    <t>Добавить в анализ дбс кол-во положительных дней</t>
+  </si>
+  <si>
+    <t>Добавить результаты тестов за последние N-дней</t>
+  </si>
+  <si>
+    <t>Почистить дбс</t>
+  </si>
+  <si>
+    <t>Что-то сделать с оптуной, что бы она не выбирала варианты с экстримальным count</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -817,7 +850,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -851,6 +884,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1259,16 +1295,19 @@
         <v>185</v>
       </c>
       <c r="S2" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="T2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="V2" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="V2" s="2" t="s">
-        <v>5</v>
+      <c r="W2" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1309,16 +1348,19 @@
         <v>214</v>
       </c>
       <c r="S3" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="V3" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="V3" s="2" t="s">
-        <v>98</v>
+      <c r="W3" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="90" x14ac:dyDescent="0.25">
@@ -1356,16 +1398,19 @@
         <v>217</v>
       </c>
       <c r="S4" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="T4" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="U4" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="V4" s="2" t="s">
-        <v>69</v>
+      <c r="W4" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1400,16 +1445,19 @@
         <v>219</v>
       </c>
       <c r="S5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="T5" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="T5" s="2" t="s">
+      <c r="U5" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="U5" s="2" t="s">
+      <c r="V5" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="V5" s="2" t="s">
-        <v>63</v>
+      <c r="W5" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1444,22 +1492,25 @@
         <v>198</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="S6" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="T6" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="U6" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="U6" s="2" t="s">
+      <c r="V6" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="V6" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+      <c r="W6" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1491,19 +1542,22 @@
         <v>199</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="S7" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="T7" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>121</v>
+      <c r="W7" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1535,22 +1589,25 @@
         <v>200</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="S8" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="U8" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="U8" s="9" t="s">
+      <c r="V8" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="V8" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+      <c r="W8" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1579,19 +1636,19 @@
         <v>201</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="U9" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="V9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V9" s="2" t="s">
-        <v>123</v>
+      <c r="W9" s="9" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1622,20 +1679,20 @@
       <c r="Q10" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="R10" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="S10" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="T10" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="U10" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="U10" s="2" t="s">
+      <c r="V10" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="V10" s="9" t="s">
-        <v>163</v>
+      <c r="W10" s="2" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1666,17 +1723,17 @@
       <c r="Q11" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="S11" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="T11" s="2" t="s">
+      <c r="R11" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="U11" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="U11" s="2" t="s">
+      <c r="V11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V11" s="2" t="s">
-        <v>169</v>
+      <c r="W11" s="2" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1707,14 +1764,17 @@
       <c r="Q12" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="S12" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="V12" s="2" t="s">
+      <c r="R12" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="W12" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1742,14 +1802,11 @@
       <c r="Q13" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="S13" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="R13" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1777,8 +1834,8 @@
       <c r="Q14" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="R14" s="7" t="s">
-        <v>210</v>
+      <c r="R14" s="4" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
@@ -1809,9 +1866,6 @@
       <c r="Q15" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="R15" s="7" t="s">
-        <v>211</v>
-      </c>
     </row>
     <row r="16" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -1832,9 +1886,6 @@
       <c r="P16" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="R16" s="4" t="s">
-        <v>212</v>
-      </c>
     </row>
     <row r="17" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -1855,9 +1906,6 @@
       <c r="P17" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="R17" s="4" t="s">
-        <v>213</v>
-      </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -1878,9 +1926,6 @@
       <c r="P18" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="R18" s="7" t="s">
-        <v>215</v>
-      </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
@@ -1901,9 +1946,6 @@
       <c r="P19" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="R19" s="4" t="s">
-        <v>216</v>
-      </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -1924,9 +1966,6 @@
       <c r="P20" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="R20" s="4" t="s">
-        <v>221</v>
-      </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -1941,9 +1980,6 @@
       <c r="P21" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="R21" s="4" t="s">
-        <v>225</v>
-      </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -1958,9 +1994,6 @@
       <c r="P22" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="R22" s="7" t="s">
-        <v>232</v>
-      </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -1975,9 +2008,6 @@
       <c r="P23" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="R23" s="7" t="s">
-        <v>233</v>
-      </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
@@ -1992,9 +2022,6 @@
       <c r="P24" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="R24" s="4" t="s">
-        <v>234</v>
-      </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
@@ -2009,9 +2036,6 @@
       <c r="P25" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="R25" s="7" t="s">
-        <v>235</v>
-      </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
@@ -2024,7 +2048,7 @@
         <v>94</v>
       </c>
       <c r="R26" s="7" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -2034,8 +2058,8 @@
       <c r="D27" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="R27" s="4" t="s">
-        <v>237</v>
+      <c r="R27" s="7" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -2046,7 +2070,7 @@
         <v>57</v>
       </c>
       <c r="R28" s="4" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -2056,6 +2080,9 @@
       <c r="D29" s="4" t="s">
         <v>58</v>
       </c>
+      <c r="R29" s="4" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
@@ -2064,6 +2091,9 @@
       <c r="D30" s="7" t="s">
         <v>59</v>
       </c>
+      <c r="R30" s="7" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
@@ -2072,6 +2102,9 @@
       <c r="D31" s="7" t="s">
         <v>60</v>
       </c>
+      <c r="R31" s="4" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
@@ -2080,86 +2113,113 @@
       <c r="D32" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="R32" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="R33" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="R34" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="R35" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="R36" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="R37" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="R38" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="R39" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="R40" s="4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705AD1C3-DFA2-443A-BEE2-71B36E61F101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBDCCBB1-D085-4C2E-A733-59661A3B6D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1495,7 +1495,7 @@
         <v>221</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="T6" s="2" t="s">
         <v>205</v>
@@ -1544,9 +1544,6 @@
       <c r="R7" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>206</v>
       </c>
@@ -1591,9 +1588,6 @@
       <c r="R8" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="S8" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="T8" s="2" t="s">
         <v>218</v>
       </c>
@@ -1838,7 +1832,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1866,8 +1860,11 @@
       <c r="Q15" s="7" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+      <c r="R15" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1885,6 +1882,9 @@
       </c>
       <c r="P16" s="4" t="s">
         <v>174</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="30" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBDCCBB1-D085-4C2E-A733-59661A3B6D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98D70F3-2795-49BD-BC7C-49C308363DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="248">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -776,6 +776,9 @@
   </si>
   <si>
     <t>Что-то сделать с оптуной, что бы она не выбирала варианты с экстримальным count</t>
+  </si>
+  <si>
+    <t>Подумать над стопом в STA3 (график растущий, но большие просадки</t>
   </si>
 </sst>
 </file>
@@ -1445,7 +1448,7 @@
         <v>219</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>5</v>
+        <v>246</v>
       </c>
       <c r="T5" s="2" t="s">
         <v>204</v>
@@ -1544,6 +1547,9 @@
       <c r="R7" s="4" t="s">
         <v>223</v>
       </c>
+      <c r="S7" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="T7" s="2" t="s">
         <v>206</v>
       </c>
@@ -1864,7 +1870,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1883,8 +1889,8 @@
       <c r="P16" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="R16" s="2" t="s">
-        <v>246</v>
+      <c r="R16" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="30" x14ac:dyDescent="0.25">
@@ -1906,6 +1912,9 @@
       <c r="P17" s="4" t="s">
         <v>176</v>
       </c>
+      <c r="R17" s="7" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -1926,6 +1935,9 @@
       <c r="P18" s="4" t="s">
         <v>165</v>
       </c>
+      <c r="R18" s="7" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
@@ -1946,6 +1958,9 @@
       <c r="P19" s="7" t="s">
         <v>166</v>
       </c>
+      <c r="R19" s="4" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -1966,6 +1981,9 @@
       <c r="P20" s="4" t="s">
         <v>170</v>
       </c>
+      <c r="R20" s="4" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -1980,6 +1998,9 @@
       <c r="P21" s="7" t="s">
         <v>171</v>
       </c>
+      <c r="R21" s="7" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -1994,6 +2015,9 @@
       <c r="P22" s="7" t="s">
         <v>172</v>
       </c>
+      <c r="R22" s="4" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -2008,6 +2032,9 @@
       <c r="P23" s="7" t="s">
         <v>173</v>
       </c>
+      <c r="R23" s="4" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
@@ -2022,6 +2049,9 @@
       <c r="P24" s="4" t="s">
         <v>178</v>
       </c>
+      <c r="R24" s="4" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
@@ -2036,6 +2066,9 @@
       <c r="P25" s="7" t="s">
         <v>180</v>
       </c>
+      <c r="R25" s="7" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
@@ -2048,7 +2081,7 @@
         <v>94</v>
       </c>
       <c r="R26" s="7" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -2058,8 +2091,8 @@
       <c r="D27" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="R27" s="7" t="s">
-        <v>211</v>
+      <c r="R27" s="4" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -2069,8 +2102,8 @@
       <c r="D28" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R28" s="4" t="s">
-        <v>212</v>
+      <c r="R28" s="7" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -2080,8 +2113,8 @@
       <c r="D29" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="R29" s="4" t="s">
-        <v>213</v>
+      <c r="R29" s="7" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -2091,8 +2124,8 @@
       <c r="D30" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="R30" s="7" t="s">
-        <v>215</v>
+      <c r="R30" s="4" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -2103,7 +2136,7 @@
         <v>60</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -2113,113 +2146,86 @@
       <c r="D32" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="R32" s="4" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="R33" s="4" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="R34" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
-      <c r="R35" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="R36" s="4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="R37" s="7" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="R38" s="7" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="R39" s="4" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="R40" s="4" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98D70F3-2795-49BD-BC7C-49C308363DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D034175-9FAC-4554-810E-368A18A95C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="253">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -779,6 +779,21 @@
   </si>
   <si>
     <t>Подумать над стопом в STA3 (график растущий, но большие просадки</t>
+  </si>
+  <si>
+    <t>Провести child_test для ликвидных акций</t>
+  </si>
+  <si>
+    <t>Провести child_test для bitget</t>
+  </si>
+  <si>
+    <t>Провести child_test для bybit</t>
+  </si>
+  <si>
+    <t>Провести child_test для потенциальных фьючерсов (SRU5,EDU5,GAZPF,SBERF,SVU5,VBU5)</t>
+  </si>
+  <si>
+    <t>Обертку n-инструментов для VT</t>
   </si>
 </sst>
 </file>
@@ -1297,19 +1312,19 @@
       <c r="R2" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="V2" s="9" t="s">
+      <c r="W2" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1350,19 +1365,19 @@
       <c r="R3" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="V3" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="X3" s="2" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1400,19 +1415,19 @@
       <c r="R4" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="U4" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1447,19 +1462,19 @@
       <c r="R5" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="T5" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="T5" s="2" t="s">
+      <c r="U5" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="U5" s="2" t="s">
+      <c r="V5" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="V5" s="2" t="s">
+      <c r="W5" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="W5" s="2" t="s">
+      <c r="X5" s="2" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1497,19 +1512,19 @@
       <c r="R6" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="U6" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="U6" s="2" t="s">
+      <c r="V6" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="W6" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="W6" s="2" t="s">
+      <c r="X6" s="2" t="s">
         <v>121</v>
       </c>
     </row>
@@ -1547,19 +1562,19 @@
       <c r="R7" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -1595,15 +1610,18 @@
         <v>227</v>
       </c>
       <c r="T8" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="U8" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="V8" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="V8" s="9" t="s">
+      <c r="W8" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="W8" s="2" t="s">
+      <c r="X8" s="2" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1639,15 +1657,18 @@
         <v>225</v>
       </c>
       <c r="T9" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="U9" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="U9" s="2" t="s">
+      <c r="V9" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="V9" s="2" t="s">
+      <c r="W9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="W9" s="9" t="s">
+      <c r="X9" s="9" t="s">
         <v>163</v>
       </c>
     </row>
@@ -1683,15 +1704,18 @@
         <v>129</v>
       </c>
       <c r="T10" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="U10" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="U10" s="2" t="s">
+      <c r="V10" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="V10" s="2" t="s">
+      <c r="W10" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="W10" s="2" t="s">
+      <c r="X10" s="2" t="s">
         <v>169</v>
       </c>
     </row>
@@ -1726,13 +1750,19 @@
       <c r="R11" s="4" t="s">
         <v>245</v>
       </c>
+      <c r="T11" s="2" t="s">
+        <v>250</v>
+      </c>
       <c r="U11" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="V11" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="V11" s="2" t="s">
+      <c r="W11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W11" s="2" t="s">
+      <c r="X11" s="2" t="s">
         <v>238</v>
       </c>
     </row>
@@ -1767,10 +1797,10 @@
       <c r="R12" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="U12" s="2" t="s">
+      <c r="V12" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="W12" s="2" t="s">
+      <c r="X12" s="2" t="s">
         <v>175</v>
       </c>
     </row>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D034175-9FAC-4554-810E-368A18A95C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E93666-71D2-4FBD-8214-49FF36ADF10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="255">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -790,10 +790,16 @@
     <t>Провести child_test для bybit</t>
   </si>
   <si>
-    <t>Провести child_test для потенциальных фьючерсов (SRU5,EDU5,GAZPF,SBERF,SVU5,VBU5)</t>
-  </si>
-  <si>
     <t>Обертку n-инструментов для VT</t>
+  </si>
+  <si>
+    <t>LTA2+ggd(внутри BB) LTA2+goose ( снаружи BB)</t>
+  </si>
+  <si>
+    <t>Добавить возмодность закрытия сделок в 2330 в optuna</t>
+  </si>
+  <si>
+    <t>Провести child_test для потенциальных фьючерсов (SRU5,EDU5,GAZPF,SBERF,SVU5,VBU5,SF,NA)</t>
   </si>
 </sst>
 </file>
@@ -818,7 +824,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -855,6 +861,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -868,7 +880,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -904,6 +916,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1269,7 +1284,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1311,6 +1326,9 @@
       </c>
       <c r="R2" s="4" t="s">
         <v>185</v>
+      </c>
+      <c r="S2" s="13" t="s">
+        <v>254</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>241</v>
@@ -1416,7 +1434,7 @@
         <v>217</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>197</v>
@@ -1463,7 +1481,7 @@
         <v>219</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="U5" s="2" t="s">
         <v>204</v>
@@ -1478,7 +1496,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1513,7 +1531,7 @@
         <v>221</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="U6" s="2" t="s">
         <v>205</v>
@@ -1563,7 +1581,7 @@
         <v>223</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>206</v>
@@ -1610,7 +1628,7 @@
         <v>227</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>218</v>
@@ -1754,7 +1772,7 @@
         <v>250</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="V11" s="2" t="s">
         <v>181</v>
@@ -1796,6 +1814,9 @@
       </c>
       <c r="R12" s="4" t="s">
         <v>239</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="V12" s="2" t="s">
         <v>186</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E93666-71D2-4FBD-8214-49FF36ADF10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDA5158-F70A-4463-BDFC-9E89DC746DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="263">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -800,6 +800,30 @@
   </si>
   <si>
     <t>Провести child_test для потенциальных фьючерсов (SRU5,EDU5,GAZPF,SBERF,SVU5,VBU5,SF,NA)</t>
+  </si>
+  <si>
+    <t>Протестить BR и NG за 3 месяца</t>
+  </si>
+  <si>
+    <t>Какой-нибудь пробойный робот с adx и осцилятором с направлением тренда</t>
+  </si>
+  <si>
+    <t>STA4 (STA3 + adx + uo (или что-то другое) + работа в боковике (ggd или bb))</t>
+  </si>
+  <si>
+    <t>ranger + anger</t>
+  </si>
+  <si>
+    <t>Подумать над obbi</t>
+  </si>
+  <si>
+    <t>Подумать над новым индикатором выгоды</t>
+  </si>
+  <si>
+    <t>Revan на нестабильном тренде, кто-то другой на стабильном.</t>
+  </si>
+  <si>
+    <t>Стопнутый GGD (стоп можно по adx или альтернативе) Можно по линии в 2х спредов)</t>
   </si>
 </sst>
 </file>
@@ -863,7 +887,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1284,7 +1308,7 @@
         <v>45908</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1327,8 +1351,8 @@
       <c r="R2" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="S2" s="13" t="s">
-        <v>254</v>
+      <c r="S2" s="4" t="s">
+        <v>253</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>241</v>
@@ -1383,6 +1407,9 @@
       <c r="R3" s="4" t="s">
         <v>214</v>
       </c>
+      <c r="S3" s="13" t="s">
+        <v>254</v>
+      </c>
       <c r="T3" s="2" t="s">
         <v>240</v>
       </c>
@@ -1433,6 +1460,9 @@
       <c r="R4" s="4" t="s">
         <v>217</v>
       </c>
+      <c r="S4" s="13" t="s">
+        <v>248</v>
+      </c>
       <c r="T4" s="2" t="s">
         <v>252</v>
       </c>
@@ -1627,6 +1657,9 @@
       <c r="R8" s="4" t="s">
         <v>227</v>
       </c>
+      <c r="S8" s="2" t="s">
+        <v>255</v>
+      </c>
       <c r="T8" s="2" t="s">
         <v>247</v>
       </c>
@@ -1675,7 +1708,7 @@
         <v>225</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>228</v>
@@ -1722,7 +1755,7 @@
         <v>129</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>230</v>
@@ -1769,7 +1802,7 @@
         <v>245</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>251</v>
@@ -1816,10 +1849,13 @@
         <v>239</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="V12" s="2" t="s">
         <v>186</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>175</v>
@@ -1856,6 +1892,9 @@
       <c r="R13" s="4" t="s">
         <v>244</v>
       </c>
+      <c r="T13" s="2" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="14" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -1888,8 +1927,11 @@
       <c r="R14" s="4" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+      <c r="T14" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1920,8 +1962,11 @@
       <c r="R15" s="4" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+      <c r="T15" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1942,6 +1987,9 @@
       </c>
       <c r="R16" s="4" t="s">
         <v>5</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="30" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDA5158-F70A-4463-BDFC-9E89DC746DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407AA081-11DD-40EE-B054-13B628D7E05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="264">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -814,9 +814,6 @@
     <t>ranger + anger</t>
   </si>
   <si>
-    <t>Подумать над obbi</t>
-  </si>
-  <si>
     <t>Подумать над новым индикатором выгоды</t>
   </si>
   <si>
@@ -824,6 +821,12 @@
   </si>
   <si>
     <t>Стопнутый GGD (стоп можно по adx или альтернативе) Можно по линии в 2х спредов)</t>
+  </si>
+  <si>
+    <t>Поискать варинты реверсных роботов под Eu,Si,ED</t>
+  </si>
+  <si>
+    <t>Подумать над obbi (возможно заработает на Si)</t>
   </si>
 </sst>
 </file>
@@ -1855,7 +1858,7 @@
         <v>186</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>175</v>
@@ -1928,7 +1931,7 @@
         <v>243</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -1963,7 +1966,7 @@
         <v>226</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -1989,10 +1992,10 @@
         <v>5</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2014,8 +2017,11 @@
       <c r="R17" s="7" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="T17" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2038,7 +2044,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2061,7 +2067,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2084,7 +2090,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2101,7 +2107,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2118,7 +2124,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2135,7 +2141,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2152,7 +2158,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2169,7 +2175,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2183,7 +2189,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2194,7 +2200,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2205,7 +2211,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2216,7 +2222,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2227,7 +2233,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2238,7 +2244,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407AA081-11DD-40EE-B054-13B628D7E05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFAFC6A-3BE8-4097-9A11-9A6D6D555E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="273">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -827,6 +827,33 @@
   </si>
   <si>
     <t>Подумать над obbi (возможно заработает на Si)</t>
+  </si>
+  <si>
+    <t>PSTA6_DODO</t>
+  </si>
+  <si>
+    <t>PSTA6_DUELDODO</t>
+  </si>
+  <si>
+    <t>Модифицировать дехаку на защиту от ШБ</t>
+  </si>
+  <si>
+    <t>PSTA6_VULTURE</t>
+  </si>
+  <si>
+    <t>PSTA6_PIGEON</t>
+  </si>
+  <si>
+    <t>PSTA6_SHERIFF</t>
+  </si>
+  <si>
+    <t>PSTA6_ADVENTURE</t>
+  </si>
+  <si>
+    <t>Анализ зигзага на 18 паттернов</t>
+  </si>
+  <si>
+    <t>Анализ зигзага на &gt;18 паттернов</t>
   </si>
 </sst>
 </file>
@@ -1513,6 +1540,9 @@
       <c r="R5" s="4" t="s">
         <v>219</v>
       </c>
+      <c r="S5" s="4" t="s">
+        <v>271</v>
+      </c>
       <c r="T5" s="2" t="s">
         <v>242</v>
       </c>
@@ -1854,6 +1884,9 @@
       <c r="T12" s="2" t="s">
         <v>257</v>
       </c>
+      <c r="U12" s="2" t="s">
+        <v>272</v>
+      </c>
       <c r="V12" s="2" t="s">
         <v>186</v>
       </c>
@@ -2017,11 +2050,14 @@
       <c r="R17" s="7" t="s">
         <v>210</v>
       </c>
+      <c r="S17" s="4" t="s">
+        <v>264</v>
+      </c>
       <c r="T17" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2042,6 +2078,12 @@
       </c>
       <c r="R18" s="7" t="s">
         <v>211</v>
+      </c>
+      <c r="S18" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -2066,6 +2108,9 @@
       <c r="R19" s="4" t="s">
         <v>212</v>
       </c>
+      <c r="S19" s="4" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -2089,6 +2134,9 @@
       <c r="R20" s="4" t="s">
         <v>213</v>
       </c>
+      <c r="S20" s="4" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -2106,6 +2154,9 @@
       <c r="R21" s="7" t="s">
         <v>215</v>
       </c>
+      <c r="S21" s="7" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -2122,6 +2173,9 @@
       </c>
       <c r="R22" s="4" t="s">
         <v>216</v>
+      </c>
+      <c r="S22" s="7" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFAFC6A-3BE8-4097-9A11-9A6D6D555E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{488299CF-9FCA-44FA-86AE-79E5E60D72C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="274">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -854,6 +854,9 @@
   </si>
   <si>
     <t>Анализ зигзага на &gt;18 паттернов</t>
+  </si>
+  <si>
+    <t>Анализ большего числа волн зигзага</t>
   </si>
 </sst>
 </file>
@@ -1931,6 +1934,9 @@
       <c r="T13" s="2" t="s">
         <v>258</v>
       </c>
+      <c r="U13" s="2" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="14" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{488299CF-9FCA-44FA-86AE-79E5E60D72C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631A83F8-F0F3-4C0C-9890-CB78EC10B496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="282">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -802,9 +802,6 @@
     <t>Провести child_test для потенциальных фьючерсов (SRU5,EDU5,GAZPF,SBERF,SVU5,VBU5,SF,NA)</t>
   </si>
   <si>
-    <t>Протестить BR и NG за 3 месяца</t>
-  </si>
-  <si>
     <t>Какой-нибудь пробойный робот с adx и осцилятором с направлением тренда</t>
   </si>
   <si>
@@ -857,6 +854,33 @@
   </si>
   <si>
     <t>Анализ большего числа волн зигзага</t>
+  </si>
+  <si>
+    <t>Изменить логику замены заявок в QT</t>
+  </si>
+  <si>
+    <t>Вернуть peacks из pattern18</t>
+  </si>
+  <si>
+    <t>Протестить BR и NG за 1.5 месяца</t>
+  </si>
+  <si>
+    <t>Ranger с разными threshold (как в DODO)</t>
+  </si>
+  <si>
+    <t>Оптимизацию RMU5 под большие комиссии</t>
+  </si>
+  <si>
+    <t>Побарный анализ (очередь из баров)</t>
+  </si>
+  <si>
+    <t>ДЛЯ ПРОВЕРКИ ОШИБКИ СТАРТА VT ВСЕГДА ИМЕТЬ ИНСТРУМЕНТ, КОТОРЫЙ НЕ ДОЛЖЕН ТОРГОВАТЬ В КОНФИГУРАЦИИ ТЕРМИНАЛА</t>
+  </si>
+  <si>
+    <t>Сделать аналоги PSTA6 на GGD вместо smas</t>
+  </si>
+  <si>
+    <t>Попробовать обновить оптуну на 2 фактора, прибыль и кол-во сделок</t>
   </si>
 </sst>
 </file>
@@ -937,7 +961,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -976,6 +1000,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1544,7 +1571,7 @@
         <v>219</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="T5" s="2" t="s">
         <v>242</v>
@@ -1596,6 +1623,9 @@
       <c r="R6" s="4" t="s">
         <v>221</v>
       </c>
+      <c r="S6" s="4" t="s">
+        <v>275</v>
+      </c>
       <c r="T6" s="2" t="s">
         <v>246</v>
       </c>
@@ -1646,6 +1676,9 @@
       <c r="R7" s="4" t="s">
         <v>223</v>
       </c>
+      <c r="S7" s="4" t="s">
+        <v>273</v>
+      </c>
       <c r="T7" s="2" t="s">
         <v>229</v>
       </c>
@@ -1662,7 +1695,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1693,8 +1726,8 @@
       <c r="R8" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="S8" s="2" t="s">
-        <v>255</v>
+      <c r="S8" s="14" t="s">
+        <v>279</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>247</v>
@@ -1743,6 +1776,9 @@
       <c r="R9" s="4" t="s">
         <v>225</v>
       </c>
+      <c r="S9" s="2" t="s">
+        <v>280</v>
+      </c>
       <c r="T9" s="2" t="s">
         <v>249</v>
       </c>
@@ -1790,6 +1826,9 @@
       <c r="R10" s="12" t="s">
         <v>129</v>
       </c>
+      <c r="S10" s="2" t="s">
+        <v>281</v>
+      </c>
       <c r="T10" s="2" t="s">
         <v>250</v>
       </c>
@@ -1838,7 +1877,7 @@
         <v>245</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>251</v>
@@ -1885,16 +1924,16 @@
         <v>239</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="V12" s="2" t="s">
         <v>186</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>175</v>
@@ -1932,10 +1971,10 @@
         <v>244</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -1970,7 +2009,10 @@
         <v>243</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -2005,7 +2047,7 @@
         <v>226</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -2031,7 +2073,7 @@
         <v>5</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="45" x14ac:dyDescent="0.25">
@@ -2057,10 +2099,10 @@
         <v>210</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="30" x14ac:dyDescent="0.25">
@@ -2086,10 +2128,10 @@
         <v>211</v>
       </c>
       <c r="S18" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="T18" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -2115,10 +2157,13 @@
         <v>212</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2141,10 +2186,13 @@
         <v>213</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2161,7 +2209,10 @@
         <v>215</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -2181,7 +2232,7 @@
         <v>216</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631A83F8-F0F3-4C0C-9890-CB78EC10B496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4F0534-9ED3-413B-87C9-389E7A8D4BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="288">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -881,6 +881,24 @@
   </si>
   <si>
     <t>Попробовать обновить оптуну на 2 фактора, прибыль и кол-во сделок</t>
+  </si>
+  <si>
+    <t>PSTA7_DODO</t>
+  </si>
+  <si>
+    <t>PSTA7_DUELDODO</t>
+  </si>
+  <si>
+    <t>PSTA7_VULTURE</t>
+  </si>
+  <si>
+    <t>PSTA7_PIGEON</t>
+  </si>
+  <si>
+    <t>PSTA7_SHERIFF</t>
+  </si>
+  <si>
+    <t>PSTA7_ADVENTURE</t>
   </si>
 </sst>
 </file>
@@ -961,7 +979,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1000,9 +1018,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1726,7 +1741,7 @@
       <c r="R8" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="S8" s="14" t="s">
+      <c r="S8" s="12" t="s">
         <v>279</v>
       </c>
       <c r="T8" s="2" t="s">
@@ -1776,7 +1791,7 @@
       <c r="R9" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="S9" s="4" t="s">
         <v>280</v>
       </c>
       <c r="T9" s="2" t="s">
@@ -2251,6 +2266,9 @@
       <c r="R23" s="4" t="s">
         <v>220</v>
       </c>
+      <c r="S23" s="4" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
@@ -2268,6 +2286,9 @@
       <c r="R24" s="4" t="s">
         <v>224</v>
       </c>
+      <c r="S24" s="7" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
@@ -2285,6 +2306,9 @@
       <c r="R25" s="7" t="s">
         <v>231</v>
       </c>
+      <c r="S25" s="7" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
@@ -2299,6 +2323,9 @@
       <c r="R26" s="7" t="s">
         <v>232</v>
       </c>
+      <c r="S26" s="7" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -2310,6 +2337,9 @@
       <c r="R27" s="4" t="s">
         <v>233</v>
       </c>
+      <c r="S27" s="7" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
@@ -2320,6 +2350,9 @@
       </c>
       <c r="R28" s="7" t="s">
         <v>234</v>
+      </c>
+      <c r="S28" s="7" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4F0534-9ED3-413B-87C9-389E7A8D4BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290ADCD8-CC74-40BD-92F4-BA7AA1A1445C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -757,9 +757,6 @@
     <t>Добавить время ошибки в QT</t>
   </si>
   <si>
-    <t>Ranger без DC, +logan, + fm_rsi, ggd (тоже самое для pta19,pta21,lta2</t>
-  </si>
-  <si>
     <t>ggd+направление</t>
   </si>
   <si>
@@ -899,6 +896,9 @@
   </si>
   <si>
     <t>PSTA7_ADVENTURE</t>
+  </si>
+  <si>
+    <t>Ranger без DC, +logan, + fm_rsi, ggd (тоже самое для pta19,pta21,lta2,pta18,pta13</t>
   </si>
 </sst>
 </file>
@@ -1427,21 +1427,21 @@
         <v>185</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="U2" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="V2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="W2" s="9" t="s">
+      <c r="X2" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1483,21 +1483,21 @@
         <v>214</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="U3" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="X3" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="Y3" s="2" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1536,21 +1536,21 @@
         <v>217</v>
       </c>
       <c r="S4" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="U4" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="V4" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="X4" s="2" t="s">
+      <c r="Y4" s="2" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1586,21 +1586,21 @@
         <v>219</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="U5" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="V5" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="V5" s="2" t="s">
+      <c r="W5" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="W5" s="2" t="s">
+      <c r="X5" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="X5" s="2" t="s">
+      <c r="Y5" s="2" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1639,21 +1639,21 @@
         <v>221</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="U6" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="V6" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="W6" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="W6" s="2" t="s">
+      <c r="X6" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="X6" s="2" t="s">
+      <c r="Y6" s="2" t="s">
         <v>121</v>
       </c>
     </row>
@@ -1692,21 +1692,21 @@
         <v>223</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="T7" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="U7" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -1742,21 +1742,21 @@
         <v>227</v>
       </c>
       <c r="S8" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="U8" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="V8" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="W8" s="9" t="s">
+      <c r="X8" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="X8" s="2" t="s">
+      <c r="Y8" s="2" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1792,21 +1792,21 @@
         <v>225</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="U9" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="V9" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="V9" s="2" t="s">
+      <c r="W9" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="W9" s="2" t="s">
+      <c r="X9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="X9" s="9" t="s">
+      <c r="Y9" s="9" t="s">
         <v>163</v>
       </c>
     </row>
@@ -1841,22 +1841,22 @@
       <c r="R10" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="S10" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>250</v>
+      <c r="S10" s="4" t="s">
+        <v>262</v>
       </c>
       <c r="U10" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="V10" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="V10" s="2" t="s">
+      <c r="W10" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="W10" s="2" t="s">
+      <c r="X10" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="X10" s="2" t="s">
+      <c r="Y10" s="2" t="s">
         <v>169</v>
       </c>
     </row>
@@ -1889,21 +1889,24 @@
         <v>194</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>255</v>
+        <v>244</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>263</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="V11" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="W11" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="W11" s="2" t="s">
+      <c r="X11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="X11" s="2" t="s">
+      <c r="Y11" s="2" t="s">
         <v>238</v>
       </c>
     </row>
@@ -1938,19 +1941,22 @@
       <c r="R12" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="T12" s="2" t="s">
-        <v>256</v>
+      <c r="S12" s="4" t="s">
+        <v>265</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="V12" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="W12" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="W12" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="X12" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y12" s="2" t="s">
         <v>175</v>
       </c>
     </row>
@@ -1983,13 +1989,16 @@
         <v>208</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>257</v>
+        <v>243</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>266</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>272</v>
+        <v>256</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="30" x14ac:dyDescent="0.25">
@@ -2021,13 +2030,16 @@
         <v>203</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>262</v>
+        <v>242</v>
+      </c>
+      <c r="S14" s="7" t="s">
+        <v>267</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>278</v>
+        <v>261</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="45" x14ac:dyDescent="0.25">
@@ -2061,8 +2073,14 @@
       <c r="R15" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="T15" s="2" t="s">
-        <v>259</v>
+      <c r="S15" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="60" x14ac:dyDescent="0.25">
@@ -2087,11 +2105,14 @@
       <c r="R16" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="T16" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+      <c r="S16" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2113,14 +2134,14 @@
       <c r="R17" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="S17" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="S17" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2142,14 +2163,14 @@
       <c r="R18" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="S18" s="4" t="s">
+      <c r="S18" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="U18" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="T18" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2171,14 +2192,14 @@
       <c r="R19" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="S19" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="S19" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2200,14 +2221,14 @@
       <c r="R20" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="S20" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="S20" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2224,13 +2245,13 @@
         <v>215</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="T21" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2246,11 +2267,8 @@
       <c r="R22" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="S22" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2266,11 +2284,8 @@
       <c r="R23" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="S23" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2286,11 +2301,8 @@
       <c r="R24" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="S24" s="7" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2306,11 +2318,8 @@
       <c r="R25" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="S25" s="7" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2323,11 +2332,8 @@
       <c r="R26" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="S26" s="7" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2337,11 +2343,8 @@
       <c r="R27" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="S27" s="7" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2351,11 +2354,8 @@
       <c r="R28" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="S28" s="7" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290ADCD8-CC74-40BD-92F4-BA7AA1A1445C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36681956-5DDC-4F4E-A22E-8D3435CD6306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="290">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -856,18 +856,12 @@
     <t>Изменить логику замены заявок в QT</t>
   </si>
   <si>
-    <t>Вернуть peacks из pattern18</t>
-  </si>
-  <si>
     <t>Протестить BR и NG за 1.5 месяца</t>
   </si>
   <si>
     <t>Ranger с разными threshold (как в DODO)</t>
   </si>
   <si>
-    <t>Оптимизацию RMU5 под большие комиссии</t>
-  </si>
-  <si>
     <t>Побарный анализ (очередь из баров)</t>
   </si>
   <si>
@@ -899,6 +893,18 @@
   </si>
   <si>
     <t>Ranger без DC, +logan, + fm_rsi, ggd (тоже самое для pta19,pta21,lta2,pta18,pta13</t>
+  </si>
+  <si>
+    <t>Стабильность MA</t>
+  </si>
+  <si>
+    <t>Реалистичный тест с лимитными заявками</t>
+  </si>
+  <si>
+    <t>Изменить pattern18 на старый паттерн, а актуальный обновлять для каждой свечи</t>
+  </si>
+  <si>
+    <t>Написать новый OT c реалистичным тестом</t>
   </si>
 </sst>
 </file>
@@ -1300,15 +1306,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y51"/>
+  <dimension ref="A1:DF51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="25" width="28.28515625" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="2"/>
+    <col min="2" max="24" width="28.28515625" style="2" customWidth="1"/>
+    <col min="25" max="25" width="28.42578125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="27.42578125" style="2" customWidth="1"/>
+    <col min="27" max="110" width="27.28515625" style="2" customWidth="1"/>
+    <col min="111" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:110" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="3">
         <v>45747</v>
@@ -1382,8 +1391,263 @@
       <c r="Y1" s="3">
         <v>45908</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+      <c r="Z1" s="3">
+        <v>45915</v>
+      </c>
+      <c r="AA1" s="3">
+        <v>45922</v>
+      </c>
+      <c r="AB1" s="3">
+        <v>45929</v>
+      </c>
+      <c r="AC1" s="3">
+        <v>45936</v>
+      </c>
+      <c r="AD1" s="3">
+        <v>45943</v>
+      </c>
+      <c r="AE1" s="3">
+        <v>45950</v>
+      </c>
+      <c r="AF1" s="3">
+        <v>45957</v>
+      </c>
+      <c r="AG1" s="3">
+        <v>45964</v>
+      </c>
+      <c r="AH1" s="3">
+        <v>45971</v>
+      </c>
+      <c r="AI1" s="3">
+        <v>45978</v>
+      </c>
+      <c r="AJ1" s="3">
+        <v>45985</v>
+      </c>
+      <c r="AK1" s="3">
+        <v>45992</v>
+      </c>
+      <c r="AL1" s="3">
+        <v>45999</v>
+      </c>
+      <c r="AM1" s="3">
+        <v>46006</v>
+      </c>
+      <c r="AN1" s="3">
+        <v>46013</v>
+      </c>
+      <c r="AO1" s="3">
+        <v>46020</v>
+      </c>
+      <c r="AP1" s="3">
+        <v>46027</v>
+      </c>
+      <c r="AQ1" s="3">
+        <v>46034</v>
+      </c>
+      <c r="AR1" s="3">
+        <v>46041</v>
+      </c>
+      <c r="AS1" s="3">
+        <v>46048</v>
+      </c>
+      <c r="AT1" s="3">
+        <v>46055</v>
+      </c>
+      <c r="AU1" s="3">
+        <v>46062</v>
+      </c>
+      <c r="AV1" s="3">
+        <v>46069</v>
+      </c>
+      <c r="AW1" s="3">
+        <v>46076</v>
+      </c>
+      <c r="AX1" s="3">
+        <v>46083</v>
+      </c>
+      <c r="AY1" s="3">
+        <v>46090</v>
+      </c>
+      <c r="AZ1" s="3">
+        <v>46097</v>
+      </c>
+      <c r="BA1" s="3">
+        <v>46104</v>
+      </c>
+      <c r="BB1" s="3">
+        <v>46111</v>
+      </c>
+      <c r="BC1" s="3">
+        <v>46118</v>
+      </c>
+      <c r="BD1" s="3">
+        <v>46125</v>
+      </c>
+      <c r="BE1" s="3">
+        <v>46132</v>
+      </c>
+      <c r="BF1" s="3">
+        <v>46139</v>
+      </c>
+      <c r="BG1" s="3">
+        <v>46146</v>
+      </c>
+      <c r="BH1" s="3">
+        <v>46153</v>
+      </c>
+      <c r="BI1" s="3">
+        <v>46160</v>
+      </c>
+      <c r="BJ1" s="3">
+        <v>46167</v>
+      </c>
+      <c r="BK1" s="3">
+        <v>46174</v>
+      </c>
+      <c r="BL1" s="3">
+        <v>46181</v>
+      </c>
+      <c r="BM1" s="3">
+        <v>46188</v>
+      </c>
+      <c r="BN1" s="3">
+        <v>46195</v>
+      </c>
+      <c r="BO1" s="3">
+        <v>46202</v>
+      </c>
+      <c r="BP1" s="3">
+        <v>46209</v>
+      </c>
+      <c r="BQ1" s="3">
+        <v>46216</v>
+      </c>
+      <c r="BR1" s="3">
+        <v>46223</v>
+      </c>
+      <c r="BS1" s="3">
+        <v>46230</v>
+      </c>
+      <c r="BT1" s="3">
+        <v>46237</v>
+      </c>
+      <c r="BU1" s="3">
+        <v>46244</v>
+      </c>
+      <c r="BV1" s="3">
+        <v>46251</v>
+      </c>
+      <c r="BW1" s="3">
+        <v>46258</v>
+      </c>
+      <c r="BX1" s="3">
+        <v>46265</v>
+      </c>
+      <c r="BY1" s="3">
+        <v>46272</v>
+      </c>
+      <c r="BZ1" s="3">
+        <v>46279</v>
+      </c>
+      <c r="CA1" s="3">
+        <v>46286</v>
+      </c>
+      <c r="CB1" s="3">
+        <v>46293</v>
+      </c>
+      <c r="CC1" s="3">
+        <v>46300</v>
+      </c>
+      <c r="CD1" s="3">
+        <v>46307</v>
+      </c>
+      <c r="CE1" s="3">
+        <v>46314</v>
+      </c>
+      <c r="CF1" s="3">
+        <v>46321</v>
+      </c>
+      <c r="CG1" s="3">
+        <v>46328</v>
+      </c>
+      <c r="CH1" s="3">
+        <v>46335</v>
+      </c>
+      <c r="CI1" s="3">
+        <v>46342</v>
+      </c>
+      <c r="CJ1" s="3">
+        <v>46349</v>
+      </c>
+      <c r="CK1" s="3">
+        <v>46356</v>
+      </c>
+      <c r="CL1" s="3">
+        <v>46363</v>
+      </c>
+      <c r="CM1" s="3">
+        <v>46370</v>
+      </c>
+      <c r="CN1" s="3">
+        <v>46377</v>
+      </c>
+      <c r="CO1" s="3">
+        <v>46384</v>
+      </c>
+      <c r="CP1" s="3">
+        <v>46391</v>
+      </c>
+      <c r="CQ1" s="3">
+        <v>46398</v>
+      </c>
+      <c r="CR1" s="3">
+        <v>46405</v>
+      </c>
+      <c r="CS1" s="3">
+        <v>46412</v>
+      </c>
+      <c r="CT1" s="3">
+        <v>46419</v>
+      </c>
+      <c r="CU1" s="3">
+        <v>46426</v>
+      </c>
+      <c r="CV1" s="3">
+        <v>46433</v>
+      </c>
+      <c r="CW1" s="3">
+        <v>46440</v>
+      </c>
+      <c r="CX1" s="3">
+        <v>46447</v>
+      </c>
+      <c r="CY1" s="3">
+        <v>46454</v>
+      </c>
+      <c r="CZ1" s="3">
+        <v>46461</v>
+      </c>
+      <c r="DA1" s="3">
+        <v>46468</v>
+      </c>
+      <c r="DB1" s="3">
+        <v>46475</v>
+      </c>
+      <c r="DC1" s="3">
+        <v>46482</v>
+      </c>
+      <c r="DD1" s="3">
+        <v>46489</v>
+      </c>
+      <c r="DE1" s="3">
+        <v>46496</v>
+      </c>
+      <c r="DF1" s="3">
+        <v>46503</v>
+      </c>
+    </row>
+    <row r="2" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1429,23 +1693,29 @@
       <c r="S2" s="4" t="s">
         <v>252</v>
       </c>
+      <c r="T2" s="4" t="s">
+        <v>287</v>
+      </c>
       <c r="U2" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="V2" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="X2" s="9" t="s">
+      <c r="Y2" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1486,22 +1756,25 @@
         <v>253</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="V3" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="W3" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="X3" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="Y3" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:110" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1539,22 +1812,25 @@
         <v>247</v>
       </c>
       <c r="U4" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="V4" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="X4" s="2" t="s">
+      <c r="Y4" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="Y4" s="2" t="s">
+      <c r="Z4" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1588,23 +1864,23 @@
       <c r="S5" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="U5" s="2" t="s">
+      <c r="V5" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="V5" s="2" t="s">
+      <c r="W5" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="W5" s="2" t="s">
+      <c r="X5" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="X5" s="2" t="s">
+      <c r="Y5" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="Y5" s="2" t="s">
+      <c r="Z5" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1639,25 +1915,25 @@
         <v>221</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="U6" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="V6" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="W6" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="W6" s="2" t="s">
+      <c r="X6" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="X6" s="2" t="s">
+      <c r="Y6" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="Y6" s="2" t="s">
+      <c r="Z6" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1694,23 +1970,23 @@
       <c r="S7" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="Y7" s="2" t="s">
+      <c r="Z7" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:110" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1742,25 +2018,25 @@
         <v>227</v>
       </c>
       <c r="S8" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="U8" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="V8" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="W8" s="2" t="s">
+      <c r="X8" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="X8" s="9" t="s">
+      <c r="Y8" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="Y8" s="2" t="s">
+      <c r="Z8" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1792,25 +2068,25 @@
         <v>225</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="U9" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="V9" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="V9" s="2" t="s">
+      <c r="W9" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="W9" s="2" t="s">
+      <c r="X9" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="X9" s="2" t="s">
+      <c r="Y9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Y9" s="9" t="s">
+      <c r="Z9" s="9" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1844,23 +2120,23 @@
       <c r="S10" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="U10" s="2" t="s">
+      <c r="V10" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="V10" s="2" t="s">
+      <c r="W10" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="W10" s="2" t="s">
+      <c r="X10" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="X10" s="2" t="s">
+      <c r="Y10" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="Y10" s="2" t="s">
+      <c r="Z10" s="2" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:110" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1894,23 +2170,23 @@
       <c r="S11" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="U11" s="2" t="s">
+      <c r="V11" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="V11" s="2" t="s">
+      <c r="W11" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="W11" s="2" t="s">
+      <c r="X11" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="X11" s="2" t="s">
+      <c r="Y11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Y11" s="2" t="s">
+      <c r="Z11" s="2" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:110" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1944,23 +2220,23 @@
       <c r="S12" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="U12" s="2" t="s">
+      <c r="V12" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="V12" s="2" t="s">
+      <c r="W12" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="W12" s="2" t="s">
+      <c r="X12" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="X12" s="2" t="s">
+      <c r="Y12" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="Y12" s="2" t="s">
+      <c r="Z12" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:110" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1994,14 +2270,14 @@
       <c r="S13" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="U13" s="2" t="s">
+      <c r="V13" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="V13" s="2" t="s">
+      <c r="W13" s="2" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:110" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -2035,14 +2311,14 @@
       <c r="S14" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="U14" s="2" t="s">
+      <c r="V14" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="V14" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="45" x14ac:dyDescent="0.25">
+      <c r="W14" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="15" spans="1:110" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -2076,14 +2352,14 @@
       <c r="S15" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="U15" s="2" t="s">
+      <c r="V15" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="V15" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="60" x14ac:dyDescent="0.25">
+      <c r="W15" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="16" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2106,13 +2382,13 @@
         <v>5</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="U16" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="V16" s="2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2135,13 +2411,13 @@
         <v>210</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="U17" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="V17" s="2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2164,13 +2440,13 @@
         <v>211</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="U18" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="V18" s="2" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2193,13 +2469,13 @@
         <v>212</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2222,13 +2498,10 @@
         <v>213</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="U20" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2245,13 +2518,10 @@
         <v>215</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="U21" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2268,7 +2538,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2285,7 +2555,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2302,7 +2572,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2319,7 +2589,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2333,7 +2603,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2344,7 +2614,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2355,7 +2625,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2366,7 +2636,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2377,7 +2647,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2388,7 +2658,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36681956-5DDC-4F4E-A22E-8D3435CD6306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4D1EB3-9A8A-475D-9CE9-540990EAFF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="293">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -905,6 +905,15 @@
   </si>
   <si>
     <t>Написать новый OT c реалистичным тестом</t>
+  </si>
+  <si>
+    <t>Полная переоптимизация под новый тест FUT</t>
+  </si>
+  <si>
+    <t>Полная переоптимизация под новый тест Stock</t>
+  </si>
+  <si>
+    <t>Полная переоптимизация под новый тест Bitget</t>
   </si>
 </sst>
 </file>
@@ -1755,8 +1764,11 @@
       <c r="S3" s="13" t="s">
         <v>253</v>
       </c>
+      <c r="T3" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="U3" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="V3" s="2" t="s">
         <v>285</v>
@@ -1811,9 +1823,6 @@
       <c r="S4" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="U4" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="V4" s="2" t="s">
         <v>251</v>
       </c>
@@ -1970,6 +1979,9 @@
       <c r="S7" s="4" t="s">
         <v>272</v>
       </c>
+      <c r="T7" s="2" t="s">
+        <v>290</v>
+      </c>
       <c r="V7" s="2" t="s">
         <v>229</v>
       </c>
@@ -2020,6 +2032,9 @@
       <c r="S8" s="12" t="s">
         <v>276</v>
       </c>
+      <c r="T8" s="2" t="s">
+        <v>291</v>
+      </c>
       <c r="V8" s="2" t="s">
         <v>246</v>
       </c>
@@ -2069,6 +2084,9 @@
       </c>
       <c r="S9" s="4" t="s">
         <v>277</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>292</v>
       </c>
       <c r="V9" s="2" t="s">
         <v>248</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4D1EB3-9A8A-475D-9CE9-540990EAFF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF20533-47A0-484D-8C04-A821620E8463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="295">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -914,6 +914,12 @@
   </si>
   <si>
     <t>Полная переоптимизация под новый тест Bitget</t>
+  </si>
+  <si>
+    <t>Функция реверса классов ws</t>
+  </si>
+  <si>
+    <t>std вокруг zz (с последним пиком)</t>
   </si>
 </sst>
 </file>
@@ -1823,6 +1829,9 @@
       <c r="S4" s="13" t="s">
         <v>247</v>
       </c>
+      <c r="T4" s="4" t="s">
+        <v>293</v>
+      </c>
       <c r="V4" s="2" t="s">
         <v>251</v>
       </c>
@@ -1872,6 +1881,9 @@
       </c>
       <c r="S5" s="4" t="s">
         <v>269</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>294</v>
       </c>
       <c r="V5" s="2" t="s">
         <v>241</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF20533-47A0-484D-8C04-A821620E8463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34E271A-F8A0-4D1C-B288-D952BCD3E1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="294">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -790,9 +790,6 @@
     <t>Обертку n-инструментов для VT</t>
   </si>
   <si>
-    <t>LTA2+ggd(внутри BB) LTA2+goose ( снаружи BB)</t>
-  </si>
-  <si>
     <t>Добавить возмодность закрытия сделок в 2330 в optuna</t>
   </si>
   <si>
@@ -817,9 +814,6 @@
     <t>Стопнутый GGD (стоп можно по adx или альтернативе) Можно по линии в 2х спредов)</t>
   </si>
   <si>
-    <t>Поискать варинты реверсных роботов под Eu,Si,ED</t>
-  </si>
-  <si>
     <t>Подумать над obbi (возможно заработает на Si)</t>
   </si>
   <si>
@@ -920,6 +914,9 @@
   </si>
   <si>
     <t>std вокруг zz (с последним пиком)</t>
+  </si>
+  <si>
+    <t>Поработать со static_channel</t>
   </si>
 </sst>
 </file>
@@ -944,7 +941,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -987,6 +984,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1000,7 +1003,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1039,6 +1042,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1706,13 +1712,13 @@
         <v>185</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="V2" s="2" t="s">
         <v>240</v>
@@ -1768,16 +1774,16 @@
         <v>214</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>196</v>
@@ -1830,10 +1836,10 @@
         <v>247</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>197</v>
@@ -1880,13 +1886,13 @@
         <v>219</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="W5" s="2" t="s">
         <v>204</v>
@@ -1901,7 +1907,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:110" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1936,10 +1942,13 @@
         <v>221</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
+      </c>
+      <c r="T6" s="14" t="s">
+        <v>194</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="W6" s="2" t="s">
         <v>205</v>
@@ -1989,13 +1998,13 @@
         <v>223</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>206</v>
@@ -2042,13 +2051,13 @@
         <v>227</v>
       </c>
       <c r="S8" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>218</v>
@@ -2095,13 +2104,13 @@
         <v>225</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>228</v>
@@ -2148,10 +2157,11 @@
         <v>129</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>262</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="T10" s="9"/>
       <c r="V10" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>230</v>
@@ -2198,10 +2208,10 @@
         <v>244</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>250</v>
@@ -2248,25 +2258,25 @@
         <v>239</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>186</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Z12" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:110" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -2298,13 +2308,16 @@
         <v>243</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:110" ht="30" x14ac:dyDescent="0.25">
@@ -2339,13 +2352,16 @@
         <v>242</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:110" ht="45" x14ac:dyDescent="0.25">
@@ -2380,16 +2396,16 @@
         <v>226</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="16" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:110" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2412,13 +2428,13 @@
         <v>5</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2441,13 +2457,10 @@
         <v>210</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2470,13 +2483,10 @@
         <v>211</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2499,13 +2509,10 @@
         <v>212</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="V19" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2528,10 +2535,10 @@
         <v>213</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2548,10 +2555,10 @@
         <v>215</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2568,7 +2575,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2585,7 +2592,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2602,7 +2609,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2619,7 +2626,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2633,7 +2640,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2644,7 +2651,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2655,7 +2662,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2666,7 +2673,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2677,7 +2684,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2688,7 +2695,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34E271A-F8A0-4D1C-B288-D952BCD3E1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83012A32-ABC8-4988-AEFB-2D84327B4A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="299">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -917,6 +917,21 @@
   </si>
   <si>
     <t>Поработать со static_channel</t>
+  </si>
+  <si>
+    <t>VSAT1_MERCURY</t>
+  </si>
+  <si>
+    <t>VSAT1_VENUS</t>
+  </si>
+  <si>
+    <t>PTA21_MALTHAEL</t>
+  </si>
+  <si>
+    <t>PTA24_BRIGHTWING</t>
+  </si>
+  <si>
+    <t>PTA24_DEATHWING</t>
   </si>
 </sst>
 </file>
@@ -1838,6 +1853,9 @@
       <c r="T4" s="4" t="s">
         <v>291</v>
       </c>
+      <c r="U4" s="2" t="s">
+        <v>290</v>
+      </c>
       <c r="V4" s="2" t="s">
         <v>241</v>
       </c>
@@ -2106,9 +2124,6 @@
       <c r="S9" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="T9" s="2" t="s">
-        <v>290</v>
-      </c>
       <c r="V9" s="2" t="s">
         <v>254</v>
       </c>
@@ -2354,6 +2369,9 @@
       <c r="S14" s="7" t="s">
         <v>265</v>
       </c>
+      <c r="T14" s="4" t="s">
+        <v>294</v>
+      </c>
       <c r="V14" s="2" t="s">
         <v>262</v>
       </c>
@@ -2398,6 +2416,9 @@
       <c r="S15" s="7" t="s">
         <v>266</v>
       </c>
+      <c r="T15" s="7" t="s">
+        <v>295</v>
+      </c>
       <c r="V15" s="2" t="s">
         <v>272</v>
       </c>
@@ -2430,11 +2451,14 @@
       <c r="S16" s="4" t="s">
         <v>277</v>
       </c>
+      <c r="T16" s="7" t="s">
+        <v>296</v>
+      </c>
       <c r="W16" s="2" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2459,8 +2483,11 @@
       <c r="S17" s="7" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T17" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2485,8 +2512,11 @@
       <c r="S18" s="7" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T18" s="7" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2512,7 +2542,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2538,7 +2568,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2558,7 +2588,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2575,7 +2605,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2592,7 +2622,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2609,7 +2639,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2626,7 +2656,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2640,7 +2670,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2651,7 +2681,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2662,7 +2692,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2673,7 +2703,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2684,7 +2714,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2695,7 +2725,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83012A32-ABC8-4988-AEFB-2D84327B4A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A7DC44-3086-4A6F-9D21-FF459F9AB117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="300">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -811,9 +811,6 @@
     <t>Revan на нестабильном тренде, кто-то другой на стабильном.</t>
   </si>
   <si>
-    <t>Стопнутый GGD (стоп можно по adx или альтернативе) Можно по линии в 2х спредов)</t>
-  </si>
-  <si>
     <t>Подумать над obbi (возможно заработает на Si)</t>
   </si>
   <si>
@@ -932,6 +929,12 @@
   </si>
   <si>
     <t>PTA24_DEATHWING</t>
+  </si>
+  <si>
+    <t>PSTA8_AVENGER</t>
+  </si>
+  <si>
+    <t>Стопнутый GGD (стоп можно по adx или альтернативе) Можно по линии в 2х спредов) Стоп можно по буфферу от последнего фрактала</t>
   </si>
 </sst>
 </file>
@@ -1730,10 +1733,10 @@
         <v>251</v>
       </c>
       <c r="T2" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="U2" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="V2" s="2" t="s">
         <v>240</v>
@@ -1792,13 +1795,13 @@
         <v>252</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>196</v>
@@ -1851,10 +1854,10 @@
         <v>247</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="V4" s="2" t="s">
         <v>241</v>
@@ -1904,10 +1907,10 @@
         <v>219</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="V5" s="2" t="s">
         <v>245</v>
@@ -1960,7 +1963,7 @@
         <v>221</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="T6" s="14" t="s">
         <v>194</v>
@@ -2016,10 +2019,10 @@
         <v>223</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>246</v>
@@ -2069,10 +2072,10 @@
         <v>227</v>
       </c>
       <c r="S8" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="V8" s="2" t="s">
         <v>253</v>
@@ -2122,7 +2125,7 @@
         <v>225</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="V9" s="2" t="s">
         <v>254</v>
@@ -2172,7 +2175,7 @@
         <v>129</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="T10" s="9"/>
       <c r="V10" s="2" t="s">
@@ -2223,10 +2226,10 @@
         <v>244</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>250</v>
@@ -2273,13 +2276,13 @@
         <v>239</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="V12" s="2" t="s">
         <v>257</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>186</v>
@@ -2291,7 +2294,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:110" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -2323,13 +2326,13 @@
         <v>243</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Y13" s="2" t="s">
         <v>248</v>
@@ -2367,16 +2370,16 @@
         <v>242</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Y14" s="2" t="s">
         <v>249</v>
@@ -2414,16 +2417,16 @@
         <v>226</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:110" ht="30" x14ac:dyDescent="0.25">
@@ -2449,13 +2452,13 @@
         <v>5</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T16" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="30" x14ac:dyDescent="0.25">
@@ -2481,10 +2484,10 @@
         <v>210</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -2510,10 +2513,10 @@
         <v>211</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="T18" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -2539,7 +2542,10 @@
         <v>212</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
+      </c>
+      <c r="T19" s="4" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -2565,7 +2571,7 @@
         <v>213</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -2585,7 +2591,7 @@
         <v>215</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A7DC44-3086-4A6F-9D21-FF459F9AB117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DBAD27F-367D-4E6F-9DDE-8E78A629A75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="301">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -862,9 +862,6 @@
     <t>Сделать аналоги PSTA6 на GGD вместо smas</t>
   </si>
   <si>
-    <t>Попробовать обновить оптуну на 2 фактора, прибыль и кол-во сделок</t>
-  </si>
-  <si>
     <t>PSTA7_DODO</t>
   </si>
   <si>
@@ -935,6 +932,12 @@
   </si>
   <si>
     <t>Стопнутый GGD (стоп можно по adx или альтернативе) Можно по линии в 2х спредов) Стоп можно по буфферу от последнего фрактала</t>
+  </si>
+  <si>
+    <t>PTA25_TASSADAR</t>
+  </si>
+  <si>
+    <t>Трейлинг-стоп</t>
   </si>
 </sst>
 </file>
@@ -1733,10 +1736,10 @@
         <v>251</v>
       </c>
       <c r="T2" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="U2" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="V2" s="2" t="s">
         <v>240</v>
@@ -1795,13 +1798,13 @@
         <v>252</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>196</v>
@@ -1854,9 +1857,6 @@
         <v>247</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="U4" s="2" t="s">
         <v>289</v>
       </c>
       <c r="V4" s="2" t="s">
@@ -1910,10 +1910,10 @@
         <v>266</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="W5" s="2" t="s">
         <v>204</v>
@@ -1969,7 +1969,7 @@
         <v>194</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="W6" s="2" t="s">
         <v>205</v>
@@ -2021,11 +2021,11 @@
       <c r="S7" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>287</v>
+      <c r="T7" s="4" t="s">
+        <v>245</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>206</v>
@@ -2074,11 +2074,11 @@
       <c r="S8" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="T8" s="2" t="s">
-        <v>288</v>
+      <c r="T8" s="14" t="s">
+        <v>286</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>218</v>
@@ -2127,8 +2127,11 @@
       <c r="S9" s="4" t="s">
         <v>274</v>
       </c>
+      <c r="T9" s="14" t="s">
+        <v>287</v>
+      </c>
       <c r="V9" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>228</v>
@@ -2177,9 +2180,11 @@
       <c r="S10" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="T10" s="9"/>
+      <c r="T10" s="4" t="s">
+        <v>282</v>
+      </c>
       <c r="V10" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>230</v>
@@ -2229,7 +2234,7 @@
         <v>260</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>250</v>
@@ -2244,7 +2249,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="12" spans="1:110" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:110" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -2279,7 +2284,7 @@
         <v>262</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="W12" s="2" t="s">
         <v>267</v>
@@ -2294,7 +2299,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:110" ht="90" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:110" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -2329,10 +2334,13 @@
         <v>263</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>299</v>
+        <v>261</v>
       </c>
       <c r="W13" s="2" t="s">
         <v>268</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>300</v>
       </c>
       <c r="Y13" s="2" t="s">
         <v>248</v>
@@ -2373,10 +2381,10 @@
         <v>264</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="W14" s="2" t="s">
         <v>272</v>
@@ -2385,7 +2393,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="15" spans="1:110" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:110" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -2420,13 +2428,10 @@
         <v>265</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16" spans="1:110" ht="30" x14ac:dyDescent="0.25">
@@ -2452,13 +2457,10 @@
         <v>5</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="T16" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="W16" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="30" x14ac:dyDescent="0.25">
@@ -2484,10 +2486,10 @@
         <v>210</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -2513,10 +2515,10 @@
         <v>211</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="T18" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -2542,10 +2544,10 @@
         <v>212</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -2571,7 +2573,10 @@
         <v>213</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -2591,7 +2596,7 @@
         <v>215</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DBAD27F-367D-4E6F-9DDE-8E78A629A75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C327B86-872F-4D41-8904-4ACAD2233920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="302">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -938,6 +938,9 @@
   </si>
   <si>
     <t>Трейлинг-стоп</t>
+  </si>
+  <si>
+    <t>Усреднение пиков ZZ или дельты ZZ с буфером внутрь</t>
   </si>
 </sst>
 </file>
@@ -962,7 +965,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1005,12 +1008,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1024,7 +1021,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1063,9 +1060,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1689,7 +1683,7 @@
         <v>46503</v>
       </c>
     </row>
-    <row r="2" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:110" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1739,7 +1733,7 @@
         <v>283</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="V2" s="2" t="s">
         <v>240</v>
@@ -1800,9 +1794,6 @@
       <c r="T3" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>288</v>
-      </c>
       <c r="V3" s="2" t="s">
         <v>281</v>
       </c>
@@ -1965,7 +1956,7 @@
       <c r="S6" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="T6" s="14" t="s">
+      <c r="T6" s="4" t="s">
         <v>194</v>
       </c>
       <c r="V6" s="2" t="s">
@@ -2074,7 +2065,7 @@
       <c r="S8" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="T8" s="14" t="s">
+      <c r="T8" s="4" t="s">
         <v>286</v>
       </c>
       <c r="V8" s="2" t="s">
@@ -2127,7 +2118,7 @@
       <c r="S9" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="T9" s="14" t="s">
+      <c r="T9" s="4" t="s">
         <v>287</v>
       </c>
       <c r="V9" s="2" t="s">
@@ -2233,6 +2224,9 @@
       <c r="S11" s="4" t="s">
         <v>260</v>
       </c>
+      <c r="T11" s="4" t="s">
+        <v>292</v>
+      </c>
       <c r="V11" s="2" t="s">
         <v>257</v>
       </c>
@@ -2283,6 +2277,9 @@
       <c r="S12" s="4" t="s">
         <v>262</v>
       </c>
+      <c r="T12" s="7" t="s">
+        <v>293</v>
+      </c>
       <c r="V12" s="2" t="s">
         <v>298</v>
       </c>
@@ -2333,6 +2330,9 @@
       <c r="S13" s="4" t="s">
         <v>263</v>
       </c>
+      <c r="T13" s="7" t="s">
+        <v>294</v>
+      </c>
       <c r="V13" s="2" t="s">
         <v>261</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>264</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="V14" s="2" t="s">
         <v>271</v>
@@ -2389,11 +2389,14 @@
       <c r="W14" s="2" t="s">
         <v>272</v>
       </c>
+      <c r="X14" s="2" t="s">
+        <v>288</v>
+      </c>
       <c r="Y14" s="2" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="15" spans="1:110" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -2428,7 +2431,10 @@
         <v>265</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>293</v>
+        <v>296</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>284</v>
       </c>
       <c r="W15" s="2" t="s">
         <v>291</v>
@@ -2459,8 +2465,8 @@
       <c r="S16" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="T16" s="7" t="s">
-        <v>294</v>
+      <c r="T16" s="4" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="30" x14ac:dyDescent="0.25">
@@ -2489,7 +2495,7 @@
         <v>276</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -2517,9 +2523,6 @@
       <c r="S18" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="T18" s="7" t="s">
-        <v>296</v>
-      </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
@@ -2546,9 +2549,6 @@
       <c r="S19" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="T19" s="4" t="s">
-        <v>297</v>
-      </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -2574,9 +2574,6 @@
       </c>
       <c r="S20" s="7" t="s">
         <v>279</v>
-      </c>
-      <c r="T20" s="4" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C327B86-872F-4D41-8904-4ACAD2233920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4AE595-59AF-424A-98AC-B059F8B20C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="304">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -941,6 +941,12 @@
   </si>
   <si>
     <t>Усреднение пиков ZZ или дельты ZZ с буфером внутрь</t>
+  </si>
+  <si>
+    <t>PSTA9_BIRDWATCHER</t>
+  </si>
+  <si>
+    <t>PSTA9_GRAVY</t>
   </si>
 </sst>
 </file>
@@ -2333,6 +2339,9 @@
       <c r="T13" s="7" t="s">
         <v>294</v>
       </c>
+      <c r="U13" s="4" t="s">
+        <v>302</v>
+      </c>
       <c r="V13" s="2" t="s">
         <v>261</v>
       </c>
@@ -2382,6 +2391,9 @@
       </c>
       <c r="T14" s="4" t="s">
         <v>295</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>303</v>
       </c>
       <c r="V14" s="2" t="s">
         <v>271</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4AE595-59AF-424A-98AC-B059F8B20C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3285E4-7650-4C03-98ED-AD30F28B72E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="310">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -947,6 +947,24 @@
   </si>
   <si>
     <t>PSTA9_GRAVY</t>
+  </si>
+  <si>
+    <t>psta9  zz_direction change c буффером снаружи</t>
+  </si>
+  <si>
+    <t>добавить новые графы в analys_dbs (максимальная просадка от лок максимума, отклонение от линейной регрессии, наклон ЛР)</t>
+  </si>
+  <si>
+    <t>ggd со сдвигом на период фрактала</t>
+  </si>
+  <si>
+    <t>Перепроверить тесты</t>
+  </si>
+  <si>
+    <t>Подумать над ZZ без перерисовки</t>
+  </si>
+  <si>
+    <t>Марковский процесс вероятностей (измерять вероятность направления по историческим данным)</t>
   </si>
 </sst>
 </file>
@@ -1689,7 +1707,7 @@
         <v>46503</v>
       </c>
     </row>
-    <row r="2" spans="1:110" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1738,22 +1756,25 @@
       <c r="T2" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="X2" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="Y2" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="Y2" s="9" t="s">
+      <c r="AB2" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1800,23 +1821,26 @@
       <c r="T3" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="U3" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="AC3" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:110" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:110" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1856,19 +1880,22 @@
       <c r="T4" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="U4" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="Y4" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="Z4" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="X4" s="2" t="s">
+      <c r="AA4" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="Y4" s="2" t="s">
+      <c r="AB4" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="Z4" s="2" t="s">
+      <c r="AC4" s="2" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1909,19 +1936,19 @@
       <c r="T5" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="V5" s="2" t="s">
+      <c r="Y5" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="W5" s="2" t="s">
+      <c r="Z5" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="X5" s="2" t="s">
+      <c r="AA5" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="Y5" s="2" t="s">
+      <c r="AB5" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="Z5" s="2" t="s">
+      <c r="AC5" s="2" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1965,19 +1992,19 @@
       <c r="T6" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="Y6" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="W6" s="2" t="s">
+      <c r="Z6" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="X6" s="2" t="s">
+      <c r="AA6" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="Y6" s="2" t="s">
+      <c r="AB6" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="Z6" s="2" t="s">
+      <c r="AC6" s="2" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2021,19 +2048,19 @@
       <c r="T7" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="Z7" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="AA7" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="Y7" s="2" t="s">
+      <c r="AB7" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="AC7" s="2" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2074,19 +2101,19 @@
       <c r="T8" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="Y8" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="W8" s="2" t="s">
+      <c r="Z8" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="X8" s="2" t="s">
+      <c r="AA8" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="Y8" s="9" t="s">
+      <c r="AB8" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="Z8" s="2" t="s">
+      <c r="AC8" s="2" t="s">
         <v>123</v>
       </c>
     </row>
@@ -2127,19 +2154,19 @@
       <c r="T9" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="V9" s="2" t="s">
+      <c r="Y9" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="W9" s="2" t="s">
+      <c r="Z9" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="X9" s="2" t="s">
+      <c r="AA9" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="Y9" s="2" t="s">
+      <c r="AB9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Z9" s="9" t="s">
+      <c r="AC9" s="9" t="s">
         <v>163</v>
       </c>
     </row>
@@ -2180,19 +2207,19 @@
       <c r="T10" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="V10" s="2" t="s">
+      <c r="Y10" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="W10" s="2" t="s">
+      <c r="Z10" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="X10" s="2" t="s">
+      <c r="AA10" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="Y10" s="2" t="s">
+      <c r="AB10" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="Z10" s="2" t="s">
+      <c r="AC10" s="2" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2233,19 +2260,19 @@
       <c r="T11" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="V11" s="2" t="s">
+      <c r="Y11" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="W11" s="2" t="s">
+      <c r="Z11" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="X11" s="2" t="s">
+      <c r="AA11" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="Y11" s="2" t="s">
+      <c r="AB11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Z11" s="2" t="s">
+      <c r="AC11" s="2" t="s">
         <v>238</v>
       </c>
     </row>
@@ -2286,19 +2313,19 @@
       <c r="T12" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="V12" s="2" t="s">
+      <c r="Y12" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="W12" s="2" t="s">
+      <c r="Z12" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="X12" s="2" t="s">
+      <c r="AA12" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="Y12" s="2" t="s">
+      <c r="AB12" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="Z12" s="2" t="s">
+      <c r="AC12" s="2" t="s">
         <v>175</v>
       </c>
     </row>
@@ -2339,19 +2366,16 @@
       <c r="T13" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="U13" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="V13" s="2" t="s">
+      <c r="Y13" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="W13" s="2" t="s">
+      <c r="Z13" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="X13" s="2" t="s">
+      <c r="AA13" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="Y13" s="2" t="s">
+      <c r="AB13" s="2" t="s">
         <v>248</v>
       </c>
     </row>
@@ -2392,19 +2416,16 @@
       <c r="T14" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="U14" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="V14" s="2" t="s">
+      <c r="Y14" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="W14" s="2" t="s">
+      <c r="Z14" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="X14" s="2" t="s">
+      <c r="AA14" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="Y14" s="2" t="s">
+      <c r="AB14" s="2" t="s">
         <v>249</v>
       </c>
     </row>
@@ -2445,14 +2466,17 @@
       <c r="T15" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="V15" s="2" t="s">
+      <c r="Y15" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="W15" s="2" t="s">
+      <c r="Z15" s="2" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="16" spans="1:110" ht="30" x14ac:dyDescent="0.25">
+      <c r="AA15" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="16" spans="1:110" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2480,8 +2504,11 @@
       <c r="T16" s="4" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="AA16" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2509,8 +2536,11 @@
       <c r="T17" s="4" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="AA17" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2535,8 +2565,11 @@
       <c r="S18" s="7" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="AA18" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2561,8 +2594,11 @@
       <c r="S19" s="7" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="AA19" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2588,7 +2624,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2608,7 +2644,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2625,7 +2661,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2642,7 +2678,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2659,7 +2695,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2676,7 +2712,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2690,7 +2726,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2701,7 +2737,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2712,7 +2748,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2723,7 +2759,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2734,7 +2770,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2745,7 +2781,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3285E4-7650-4C03-98ED-AD30F28B72E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF16A015-89F4-490D-897A-85081BED06D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="315">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -244,9 +244,6 @@
     <t>Разделить минутки и 5-минутки в wss moex</t>
   </si>
   <si>
-    <t>Увеличить количество сделко GOLDENMEAN</t>
-  </si>
-  <si>
     <t>Провести оптимизацию под минутки</t>
   </si>
   <si>
@@ -781,12 +778,6 @@
     <t>Провести child_test для ликвидных акций</t>
   </si>
   <si>
-    <t>Провести child_test для bitget</t>
-  </si>
-  <si>
-    <t>Провести child_test для bybit</t>
-  </si>
-  <si>
     <t>Обертку n-инструментов для VT</t>
   </si>
   <si>
@@ -901,9 +892,6 @@
     <t>Полная переоптимизация под новый тест Stock</t>
   </si>
   <si>
-    <t>Полная переоптимизация под новый тест Bitget</t>
-  </si>
-  <si>
     <t>Функция реверса классов ws</t>
   </si>
   <si>
@@ -958,13 +946,40 @@
     <t>ggd со сдвигом на период фрактала</t>
   </si>
   <si>
-    <t>Перепроверить тесты</t>
-  </si>
-  <si>
     <t>Подумать над ZZ без перерисовки</t>
   </si>
   <si>
     <t>Марковский процесс вероятностей (измерять вероятность направления по историческим данным)</t>
+  </si>
+  <si>
+    <t>RNN</t>
+  </si>
+  <si>
+    <t>GRU</t>
+  </si>
+  <si>
+    <t>LSTM</t>
+  </si>
+  <si>
+    <t>Informer</t>
+  </si>
+  <si>
+    <t>Autoinformer</t>
+  </si>
+  <si>
+    <t>Transformer</t>
+  </si>
+  <si>
+    <t>TCN</t>
+  </si>
+  <si>
+    <t>ResNets</t>
+  </si>
+  <si>
+    <t>Bi-Directional Rnn Lstm</t>
+  </si>
+  <si>
+    <t>Провести оптимизацию под 30m для Bitget и Bybit</t>
   </si>
 </sst>
 </file>
@@ -989,7 +1004,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1032,6 +1047,36 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1045,7 +1090,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1071,9 +1116,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1084,6 +1126,21 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1707,7 +1764,7 @@
         <v>46503</v>
       </c>
     </row>
-    <row r="2" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:110" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1721,61 +1778,64 @@
         <v>39</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>42</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>100</v>
-      </c>
       <c r="K2" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>48</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="U2" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="Y2" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="X2" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="Z2" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AB2" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>98</v>
+        <v>305</v>
+      </c>
+      <c r="AB2" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="AC2" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="AD2" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="AE2" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="AF2" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:110" ht="60" x14ac:dyDescent="0.25">
@@ -1792,52 +1852,58 @@
         <v>40</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="S3" s="13" t="s">
-        <v>252</v>
+        <v>213</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>249</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>281</v>
+        <v>314</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>69</v>
+        <v>306</v>
+      </c>
+      <c r="AB3" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="AC3" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="AD3" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="AE3" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="AF3" s="14" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:110" ht="105" x14ac:dyDescent="0.25">
@@ -1854,49 +1920,52 @@
         <v>30</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K4" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="O4" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="S4" s="13" t="s">
-        <v>247</v>
+        <v>216</v>
+      </c>
+      <c r="S4" s="12" t="s">
+        <v>246</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="Y4" s="2" t="s">
-        <v>241</v>
+        <v>299</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB4" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AC4" s="2" t="s">
-        <v>63</v>
+        <v>307</v>
+      </c>
+      <c r="AB4" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="AC4" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AD4" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE4" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF4" s="16" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:110" ht="60" x14ac:dyDescent="0.25">
@@ -1913,46 +1982,49 @@
         <v>32</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>229</v>
+        <v>286</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="AB5" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="AC5" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:110" ht="45" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+      <c r="AB5" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="AC5" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD5" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="AE5" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="AF5" s="14" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1966,45 +2038,48 @@
         <v>33</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y6" s="2" t="s">
-        <v>246</v>
+        <v>193</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA6" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="AB6" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="AC6" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="AB6" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="AC6" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="AD6" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE6" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF6" s="13" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2022,45 +2097,48 @@
         <v>36</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="Y7" s="2" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AB7" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="AC7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="AB7" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="AC7" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="AD7" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE7" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="AF7" s="13" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2078,46 +2156,49 @@
         <v>38</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="S8" s="12" t="s">
-        <v>273</v>
+        <v>226</v>
+      </c>
+      <c r="S8" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>254</v>
+        <v>283</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="AA8" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB8" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="AC8" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="AD8" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE8" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="AB8" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC8" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:110" ht="60" x14ac:dyDescent="0.25">
+      <c r="AF8" s="15" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:110" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -2131,43 +2212,46 @@
         <v>43</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="Y9" s="2" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="AA9" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="AB9" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="AB9" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="AC9" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="AD9" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="AE9" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="AC9" s="9" t="s">
-        <v>163</v>
+      <c r="AF9" s="14" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:110" ht="60" x14ac:dyDescent="0.25">
@@ -2184,43 +2268,46 @@
         <v>46</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="R10" s="12" t="s">
-        <v>129</v>
+        <v>201</v>
+      </c>
+      <c r="R10" s="11" t="s">
+        <v>128</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="Y10" s="2" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="AA10" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="AB10" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="AC10" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="AD10" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE10" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="AB10" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC10" s="2" t="s">
-        <v>169</v>
+      <c r="AF10" s="13" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:110" ht="45" x14ac:dyDescent="0.25">
@@ -2237,43 +2324,43 @@
         <v>47</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="Y11" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="Z11" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="AA11" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AB11" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB11" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="AC11" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="AD11" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="AE11" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AC11" s="2" t="s">
-        <v>238</v>
+      <c r="AF11" s="14" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:110" ht="90" x14ac:dyDescent="0.25">
@@ -2290,46 +2377,43 @@
         <v>49</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="Y12" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="Z12" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="AA12" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="AB12" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="AC12" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:110" ht="30" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+      <c r="AB12" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="AC12" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="AD12" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="AE12" s="14" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" spans="1:110" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -2343,40 +2427,40 @@
         <v>62</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="Y13" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z13" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="AA13" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="AB13" s="2" t="s">
-        <v>248</v>
+        <v>290</v>
+      </c>
+      <c r="AB13" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="AC13" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="AD13" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="AE13" s="13" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="14" spans="1:110" ht="30" x14ac:dyDescent="0.25">
@@ -2393,40 +2477,37 @@
         <v>50</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="Y14" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="Z14" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="AA14" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="AB14" s="2" t="s">
-        <v>249</v>
+        <v>291</v>
+      </c>
+      <c r="AB14" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="AC14" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="AD14" s="14" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:110" ht="60" x14ac:dyDescent="0.25">
@@ -2443,40 +2524,40 @@
         <v>61</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="Y15" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="Z15" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="AA15" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="16" spans="1:110" ht="90" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+      <c r="AB15" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="AC15" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="AD15" s="14" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="16" spans="1:110" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2487,28 +2568,28 @@
         <v>66</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R16" s="4" t="s">
         <v>5</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="AA16" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+      <c r="AD16" s="17" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2519,28 +2600,25 @@
         <v>68</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="R17" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="AA17" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2551,25 +2629,22 @@
         <v>37</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="R18" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA18" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2580,25 +2655,22 @@
         <v>44</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA19" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2609,22 +2681,22 @@
         <v>45</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2632,19 +2704,19 @@
         <v>65</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2652,16 +2724,16 @@
         <v>51</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2669,16 +2741,16 @@
         <v>52</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2686,16 +2758,16 @@
         <v>53</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2703,16 +2775,16 @@
         <v>54</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2720,13 +2792,13 @@
         <v>55</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R26" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2734,10 +2806,10 @@
         <v>56</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2745,10 +2817,10 @@
         <v>57</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2756,10 +2828,10 @@
         <v>58</v>
       </c>
       <c r="R29" s="7" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2767,10 +2839,10 @@
         <v>59</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2778,10 +2850,10 @@
         <v>60</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2898,25 +2970,25 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="11"/>
-    <col min="2" max="2" width="54.85546875" style="10" customWidth="1"/>
-    <col min="3" max="3" width="45.140625" style="10" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="10"/>
+    <col min="2" max="2" width="54.85546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="45.140625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="10">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>136</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF16A015-89F4-490D-897A-85081BED06D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C12082-73F2-41B3-8C21-169C40788B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="316">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -980,6 +980,9 @@
   </si>
   <si>
     <t>Провести оптимизацию под 30m для Bitget и Bybit</t>
+  </si>
+  <si>
+    <t>Удалить данные 17.09 по фьючам с ошибочной 3-4 процентной сделкой</t>
   </si>
 </sst>
 </file>
@@ -1820,6 +1823,9 @@
         <v>301</v>
       </c>
       <c r="Z2" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="AA2" s="2" t="s">
         <v>305</v>
       </c>
       <c r="AB2" s="13" t="s">
@@ -1884,10 +1890,10 @@
       <c r="U3" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="Y3" s="2" t="s">
-        <v>314</v>
-      </c>
       <c r="Z3" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="AA3" s="2" t="s">
         <v>306</v>
       </c>
       <c r="AB3" s="14" t="s">
@@ -1949,7 +1955,7 @@
       <c r="U4" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="Z4" s="2" t="s">
+      <c r="AA4" s="2" t="s">
         <v>307</v>
       </c>
       <c r="AB4" s="13" t="s">
@@ -2005,7 +2011,7 @@
       <c r="T5" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="Z5" s="2" t="s">
+      <c r="AA5" s="2" t="s">
         <v>308</v>
       </c>
       <c r="AB5" s="14" t="s">
@@ -2064,7 +2070,7 @@
       <c r="T6" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="Z6" s="2" t="s">
+      <c r="AA6" s="2" t="s">
         <v>309</v>
       </c>
       <c r="AB6" s="14" t="s">
@@ -2123,7 +2129,7 @@
       <c r="T7" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="AA7" s="2" t="s">
         <v>310</v>
       </c>
       <c r="AB7" s="14" t="s">
@@ -2179,7 +2185,7 @@
       <c r="T8" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="Z8" s="2" t="s">
+      <c r="AA8" s="2" t="s">
         <v>311</v>
       </c>
       <c r="AB8" s="14" t="s">
@@ -2235,7 +2241,7 @@
       <c r="T9" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="Z9" s="2" t="s">
+      <c r="AA9" s="2" t="s">
         <v>312</v>
       </c>
       <c r="AB9" s="13" t="s">
@@ -2291,7 +2297,7 @@
       <c r="T10" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="Z10" s="2" t="s">
+      <c r="AA10" s="2" t="s">
         <v>313</v>
       </c>
       <c r="AB10" s="15" t="s">

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C12082-73F2-41B3-8C21-169C40788B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6955422-C84C-4492-B7AD-7F047E6233E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="322">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -983,6 +983,24 @@
   </si>
   <si>
     <t>Удалить данные 17.09 по фьючам с ошибочной 3-4 процентной сделкой</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Волатильность! Нужно измерять расстояние за n-баров. И выставлять подобные границы от среднего с дельтой. </t>
+  </si>
+  <si>
+    <t>Еще можно измерять максимальный ход в обе стороны. И от этого строить канал</t>
+  </si>
+  <si>
+    <t>Avenger только по боковикам</t>
+  </si>
+  <si>
+    <t>Создать древо развития роботов. Посмотреть кто с кем смешался и как можно было бы улучшить роботов</t>
+  </si>
+  <si>
+    <t>Идеи улучшений каждого действующего робота</t>
+  </si>
+  <si>
+    <t>Есть теория, что child test имеет проблемы во второй половине</t>
   </si>
 </sst>
 </file>
@@ -1822,26 +1840,32 @@
       <c r="Y2" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" s="4" t="s">
         <v>314</v>
       </c>
       <c r="AA2" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="AB2" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="AB2" s="13" t="s">
+      <c r="AC2" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="AC2" s="14" t="s">
+      <c r="AD2" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="AD2" s="13" t="s">
+      <c r="AE2" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="AE2" s="15" t="s">
+      <c r="AF2" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="AF2" s="13" t="s">
+      <c r="AG2" s="13" t="s">
         <v>97</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:110" ht="60" x14ac:dyDescent="0.25">
@@ -1890,25 +1914,28 @@
       <c r="U3" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="Z3" s="4" t="s">
         <v>315</v>
       </c>
       <c r="AA3" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="AB3" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="AB3" s="14" t="s">
+      <c r="AC3" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="AC3" s="16" t="s">
+      <c r="AD3" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="AD3" s="13" t="s">
+      <c r="AE3" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="AE3" s="16" t="s">
+      <c r="AF3" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="AF3" s="14" t="s">
+      <c r="AG3" s="14" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1956,21 +1983,24 @@
         <v>299</v>
       </c>
       <c r="AA4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AB4" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="AB4" s="13" t="s">
+      <c r="AC4" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="AC4" s="15" t="s">
+      <c r="AD4" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AD4" s="13" t="s">
+      <c r="AE4" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="AE4" s="16" t="s">
+      <c r="AF4" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="AF4" s="16" t="s">
+      <c r="AG4" s="16" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2012,21 +2042,24 @@
         <v>286</v>
       </c>
       <c r="AA5" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="AB5" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="AB5" s="14" t="s">
+      <c r="AC5" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="AC5" s="15" t="s">
+      <c r="AD5" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="AD5" s="13" t="s">
+      <c r="AE5" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="AE5" s="16" t="s">
+      <c r="AF5" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="AF5" s="14" t="s">
+      <c r="AG5" s="14" t="s">
         <v>120</v>
       </c>
     </row>
@@ -2071,21 +2104,24 @@
         <v>193</v>
       </c>
       <c r="AA6" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="AB6" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="AB6" s="14" t="s">
+      <c r="AC6" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="AC6" s="15" t="s">
+      <c r="AD6" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="AD6" s="13" t="s">
+      <c r="AE6" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="AE6" s="15" t="s">
+      <c r="AF6" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="AF6" s="13" t="s">
+      <c r="AG6" s="13" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2129,22 +2165,22 @@
       <c r="T7" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="AA7" s="2" t="s">
+      <c r="AB7" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="AB7" s="14" t="s">
+      <c r="AC7" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="AC7" s="15" t="s">
+      <c r="AD7" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="AD7" s="13" t="s">
+      <c r="AE7" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="AE7" s="13" t="s">
+      <c r="AF7" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="AF7" s="13" t="s">
+      <c r="AG7" s="13" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2185,22 +2221,22 @@
       <c r="T8" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="AA8" s="2" t="s">
+      <c r="AB8" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="AB8" s="14" t="s">
+      <c r="AC8" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="AC8" s="14" t="s">
+      <c r="AD8" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="AD8" s="13" t="s">
+      <c r="AE8" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="AE8" s="14" t="s">
+      <c r="AF8" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="AF8" s="15" t="s">
+      <c r="AG8" s="15" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2241,22 +2277,22 @@
       <c r="T9" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="AA9" s="2" t="s">
+      <c r="AB9" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="AB9" s="13" t="s">
+      <c r="AC9" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="AC9" s="14" t="s">
+      <c r="AD9" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="AD9" s="14" t="s">
+      <c r="AE9" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="AE9" s="13" t="s">
+      <c r="AF9" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="AF9" s="14" t="s">
+      <c r="AG9" s="14" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2297,22 +2333,22 @@
       <c r="T10" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="AA10" s="2" t="s">
+      <c r="AB10" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="AB10" s="15" t="s">
+      <c r="AC10" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="AC10" s="15" t="s">
+      <c r="AD10" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="AD10" s="14" t="s">
+      <c r="AE10" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="AE10" s="13" t="s">
+      <c r="AF10" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="AF10" s="13" t="s">
+      <c r="AG10" s="13" t="s">
         <v>237</v>
       </c>
     </row>
@@ -2353,19 +2389,19 @@
       <c r="T11" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="AB11" s="15" t="s">
+      <c r="AC11" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="AC11" s="15" t="s">
+      <c r="AD11" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="AD11" s="14" t="s">
+      <c r="AE11" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="AE11" s="13" t="s">
+      <c r="AF11" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AF11" s="14" t="s">
+      <c r="AG11" s="14" t="s">
         <v>174</v>
       </c>
     </row>
@@ -2406,16 +2442,16 @@
       <c r="T12" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="AB12" s="16" t="s">
+      <c r="AC12" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="AC12" s="14" t="s">
+      <c r="AD12" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="AD12" s="15" t="s">
+      <c r="AE12" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="AE12" s="14" t="s">
+      <c r="AF12" s="14" t="s">
         <v>253</v>
       </c>
     </row>
@@ -2456,16 +2492,16 @@
       <c r="T13" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="AB13" s="15" t="s">
+      <c r="AC13" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="AC13" s="14" t="s">
+      <c r="AD13" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="AD13" s="16" t="s">
+      <c r="AE13" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="AE13" s="13" t="s">
+      <c r="AF13" s="13" t="s">
         <v>304</v>
       </c>
     </row>
@@ -2506,13 +2542,13 @@
       <c r="T14" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="AB14" s="15" t="s">
+      <c r="AC14" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="AC14" s="16" t="s">
+      <c r="AD14" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="AD14" s="14" t="s">
+      <c r="AE14" s="14" t="s">
         <v>300</v>
       </c>
     </row>
@@ -2553,13 +2589,13 @@
       <c r="T15" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="AB15" s="13" t="s">
+      <c r="AC15" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="AC15" s="15" t="s">
+      <c r="AD15" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="AD15" s="14" t="s">
+      <c r="AE15" s="14" t="s">
         <v>302</v>
       </c>
     </row>
@@ -2591,7 +2627,7 @@
       <c r="T16" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="AD16" s="17" t="s">
+      <c r="AE16" s="17" t="s">
         <v>303</v>
       </c>
     </row>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6955422-C84C-4492-B7AD-7F047E6233E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EDAD10-035D-4480-8637-6994A02DAD7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="324">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1001,6 +1001,12 @@
   </si>
   <si>
     <t>Есть теория, что child test имеет проблемы во второй половине</t>
+  </si>
+  <si>
+    <t>Мультитаймфреймовые роботы</t>
+  </si>
+  <si>
+    <t>Мультипозиционные роботы</t>
   </si>
 </sst>
 </file>
@@ -1982,6 +1988,9 @@
       <c r="U4" s="7" t="s">
         <v>299</v>
       </c>
+      <c r="Z4" s="4" t="s">
+        <v>320</v>
+      </c>
       <c r="AA4" s="2" t="s">
         <v>318</v>
       </c>
@@ -2041,9 +2050,6 @@
       <c r="T5" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="AA5" s="2" t="s">
-        <v>320</v>
-      </c>
       <c r="AB5" s="2" t="s">
         <v>308</v>
       </c>
@@ -2165,6 +2171,9 @@
       <c r="T7" s="4" t="s">
         <v>244</v>
       </c>
+      <c r="AA7" s="17" t="s">
+        <v>322</v>
+      </c>
       <c r="AB7" s="2" t="s">
         <v>310</v>
       </c>
@@ -2220,6 +2229,9 @@
       </c>
       <c r="T8" s="4" t="s">
         <v>283</v>
+      </c>
+      <c r="AA8" s="17" t="s">
+        <v>323</v>
       </c>
       <c r="AB8" s="2" t="s">
         <v>311</v>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EDAD10-035D-4480-8637-6994A02DAD7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BF6EE4-C99B-4359-A506-7972CB7182D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="328">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -994,9 +994,6 @@
     <t>Avenger только по боковикам</t>
   </si>
   <si>
-    <t>Создать древо развития роботов. Посмотреть кто с кем смешался и как можно было бы улучшить роботов</t>
-  </si>
-  <si>
     <t>Идеи улучшений каждого действующего робота</t>
   </si>
   <si>
@@ -1007,6 +1004,21 @@
   </si>
   <si>
     <t>Мультипозиционные роботы</t>
+  </si>
+  <si>
+    <t>Разобраться со стопами VSAT</t>
+  </si>
+  <si>
+    <t>Парные роботы (арбитраж, сеточная реверс стратегия)</t>
+  </si>
+  <si>
+    <t>RSI-матрингейл (МПР)</t>
+  </si>
+  <si>
+    <t>MP_LTA_SHCHI</t>
+  </si>
+  <si>
+    <t>Тест для MPTA</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1043,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1104,6 +1116,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1117,7 +1135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1168,6 +1186,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1849,29 +1870,29 @@
       <c r="Z2" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AA2" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="AB2" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="AC2" s="13" t="s">
+      <c r="AD2" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="AD2" s="14" t="s">
+      <c r="AE2" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="AE2" s="13" t="s">
+      <c r="AF2" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="AF2" s="15" t="s">
+      <c r="AG2" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="AG2" s="13" t="s">
+      <c r="AH2" s="13" t="s">
         <v>97</v>
-      </c>
-      <c r="AH2" s="2" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:110" ht="60" x14ac:dyDescent="0.25">
@@ -1923,25 +1944,28 @@
       <c r="Z3" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AA3" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="AB3" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AC3" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="AC3" s="14" t="s">
+      <c r="AD3" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="AD3" s="16" t="s">
+      <c r="AE3" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="AE3" s="13" t="s">
+      <c r="AF3" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="AF3" s="16" t="s">
+      <c r="AG3" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="AG3" s="14" t="s">
+      <c r="AH3" s="14" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1989,27 +2013,27 @@
         <v>299</v>
       </c>
       <c r="Z4" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="AA4" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="AB4" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="AB4" s="2" t="s">
+      <c r="AC4" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="AC4" s="13" t="s">
+      <c r="AD4" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="AD4" s="15" t="s">
+      <c r="AE4" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AE4" s="13" t="s">
+      <c r="AF4" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="AF4" s="16" t="s">
+      <c r="AG4" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="AG4" s="16" t="s">
+      <c r="AH4" s="16" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2051,21 +2075,24 @@
         <v>286</v>
       </c>
       <c r="AB5" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="AC5" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="AC5" s="14" t="s">
+      <c r="AD5" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="AD5" s="15" t="s">
+      <c r="AE5" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="AE5" s="13" t="s">
+      <c r="AF5" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="AF5" s="16" t="s">
+      <c r="AG5" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="AG5" s="14" t="s">
+      <c r="AH5" s="14" t="s">
         <v>120</v>
       </c>
     </row>
@@ -2109,25 +2136,28 @@
       <c r="T6" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="AA6" s="2" t="s">
-        <v>321</v>
+      <c r="AA6" s="4" t="s">
+        <v>326</v>
       </c>
       <c r="AB6" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="AC6" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="AC6" s="14" t="s">
+      <c r="AD6" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="AD6" s="15" t="s">
+      <c r="AE6" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="AE6" s="13" t="s">
+      <c r="AF6" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="AF6" s="15" t="s">
+      <c r="AG6" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="AG6" s="13" t="s">
+      <c r="AH6" s="13" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2171,25 +2201,25 @@
       <c r="T7" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="AA7" s="17" t="s">
-        <v>322</v>
-      </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AB7" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="AC7" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="AC7" s="14" t="s">
+      <c r="AD7" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="AD7" s="15" t="s">
+      <c r="AE7" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="AE7" s="13" t="s">
+      <c r="AF7" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="AF7" s="13" t="s">
+      <c r="AG7" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="AG7" s="13" t="s">
+      <c r="AH7" s="13" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2230,25 +2260,25 @@
       <c r="T8" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="AA8" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="AB8" s="2" t="s">
+      <c r="AB8" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="AC8" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="AC8" s="14" t="s">
+      <c r="AD8" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="AD8" s="14" t="s">
+      <c r="AE8" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="AE8" s="13" t="s">
+      <c r="AF8" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="AF8" s="14" t="s">
+      <c r="AG8" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="AG8" s="15" t="s">
+      <c r="AH8" s="15" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2289,22 +2319,25 @@
       <c r="T9" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="AB9" s="2" t="s">
+      <c r="AB9" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="AC9" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="AC9" s="13" t="s">
+      <c r="AD9" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="AD9" s="14" t="s">
+      <c r="AE9" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="AE9" s="14" t="s">
+      <c r="AF9" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="AF9" s="13" t="s">
+      <c r="AG9" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="AG9" s="14" t="s">
+      <c r="AH9" s="14" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2345,22 +2378,22 @@
       <c r="T10" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="AB10" s="2" t="s">
+      <c r="AC10" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="AC10" s="15" t="s">
+      <c r="AD10" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="AD10" s="15" t="s">
+      <c r="AE10" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="AE10" s="14" t="s">
+      <c r="AF10" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="AF10" s="13" t="s">
+      <c r="AG10" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="AG10" s="13" t="s">
+      <c r="AH10" s="13" t="s">
         <v>237</v>
       </c>
     </row>
@@ -2401,19 +2434,19 @@
       <c r="T11" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="AC11" s="15" t="s">
+      <c r="AD11" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="AD11" s="15" t="s">
+      <c r="AE11" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="AE11" s="14" t="s">
+      <c r="AF11" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="AF11" s="13" t="s">
+      <c r="AG11" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AG11" s="14" t="s">
+      <c r="AH11" s="14" t="s">
         <v>174</v>
       </c>
     </row>
@@ -2454,16 +2487,16 @@
       <c r="T12" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="AC12" s="16" t="s">
+      <c r="AD12" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="AD12" s="14" t="s">
+      <c r="AE12" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="AE12" s="15" t="s">
+      <c r="AF12" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="AF12" s="14" t="s">
+      <c r="AG12" s="14" t="s">
         <v>253</v>
       </c>
     </row>
@@ -2504,16 +2537,16 @@
       <c r="T13" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="AC13" s="15" t="s">
+      <c r="AD13" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="AD13" s="14" t="s">
+      <c r="AE13" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="AE13" s="16" t="s">
+      <c r="AF13" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="AF13" s="13" t="s">
+      <c r="AG13" s="13" t="s">
         <v>304</v>
       </c>
     </row>
@@ -2554,13 +2587,13 @@
       <c r="T14" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="AC14" s="15" t="s">
+      <c r="AD14" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="AD14" s="16" t="s">
+      <c r="AE14" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="AE14" s="14" t="s">
+      <c r="AF14" s="14" t="s">
         <v>300</v>
       </c>
     </row>
@@ -2601,13 +2634,13 @@
       <c r="T15" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="AC15" s="13" t="s">
+      <c r="AD15" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="AD15" s="15" t="s">
+      <c r="AE15" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="AE15" s="14" t="s">
+      <c r="AF15" s="14" t="s">
         <v>302</v>
       </c>
     </row>
@@ -2639,7 +2672,7 @@
       <c r="T16" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="AE16" s="17" t="s">
+      <c r="AF16" s="17" t="s">
         <v>303</v>
       </c>
     </row>

--- a/_other/WeekPlan.xlsx
+++ b/_other/WeekPlan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\_other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BF6EE4-C99B-4359-A506-7972CB7182D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2AA7701-459D-4D13-8F68-86E0D375882E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="333">
   <si>
     <t>Новый тест с использованием БД</t>
   </si>
@@ -1019,6 +1019,21 @@
   </si>
   <si>
     <t>Тест для MPTA</t>
+  </si>
+  <si>
+    <t>записать видео 1г,2г,5л,10л</t>
+  </si>
+  <si>
+    <t>Проблема неверных позиций в QT</t>
+  </si>
+  <si>
+    <t>Начать RL2</t>
+  </si>
+  <si>
+    <t>Получать подтверждение выставления и снятия заявки для решения проблем с квиком</t>
+  </si>
+  <si>
+    <t>Пока не подтверждено снятие заявки, новую не высталять.</t>
   </si>
 </sst>
 </file>
@@ -1043,7 +1058,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1116,12 +1131,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1135,7 +1144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1186,9 +1195,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1870,28 +1876,31 @@
       <c r="Z2" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="AA2" s="18" t="s">
+      <c r="AA2" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="AG2" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="AD2" s="13" t="s">
+      <c r="AI2" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="AE2" s="14" t="s">
+      <c r="AJ2" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="AF2" s="13" t="s">
+      <c r="AK2" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="AG2" s="15" t="s">
+      <c r="AL2" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="AH2" s="13" t="s">
+      <c r="AM2" s="13" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1944,28 +1953,31 @@
       <c r="Z3" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="AA3" s="18" t="s">
+      <c r="AA3" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AE3" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="AG3" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AH3" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="AD3" s="14" t="s">
+      <c r="AI3" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="AE3" s="16" t="s">
+      <c r="AJ3" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="AF3" s="13" t="s">
+      <c r="AK3" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="AG3" s="16" t="s">
+      <c r="AL3" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="AH3" s="14" t="s">
+      <c r="AM3" s="14" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2015,25 +2027,28 @@
       <c r="Z4" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="AB4" s="2" t="s">
+      <c r="AE4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="AG4" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="AC4" s="2" t="s">
+      <c r="AH4" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="AD4" s="13" t="s">
+      <c r="AI4" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="AE4" s="15" t="s">
+      <c r="AJ4" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AF4" s="13" t="s">
+      <c r="AK4" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="AG4" s="16" t="s">
+      <c r="AL4" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="AH4" s="16" t="s">
+      <c r="AM4" s="16" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2074,25 +2089,25 @@
       <c r="T5" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="AB5" s="2" t="s">
+      <c r="AG5" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="AC5" s="2" t="s">
+      <c r="AH5" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="AD5" s="14" t="s">
+      <c r="AI5" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="AE5" s="15" t="s">
+      <c r="AJ5" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="AF5" s="13" t="s">
+      <c r="AK5" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="AG5" s="16" t="s">
+      <c r="AL5" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="AH5" s="14" t="s">
+      <c r="AM5" s="14" t="s">
         <v>120</v>
       </c>
     </row>
@@ -2139,25 +2154,25 @@
       <c r="AA6" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="AB6" s="2" t="s">
+      <c r="AG6" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="AC6" s="2" t="s">
+      <c r="AH6" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="AD6" s="14" t="s">
+      <c r="AI6" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="AE6" s="15" t="s">
+      <c r="AJ6" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="AF6" s="13" t="s">
+      <c r="AK6" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="AG6" s="15" t="s">
+      <c r="AL6" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="AH6" s="13" t="s">
+      <c r="AM6" s="13" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2201,25 +2216,25 @@
       <c r="T7" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="AB7" s="17" t="s">
+      <c r="AG7" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AH7" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="AD7" s="14" t="s">
+      <c r="AI7" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="AE7" s="15" t="s">
+      <c r="AJ7" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="AF7" s="13" t="s">
+      <c r="AK7" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="AG7" s="13" t="s">
+      <c r="AL7" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="AH7" s="13" t="s">
+      <c r="AM7" s="13" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2260,25 +2275,25 @@
       <c r="T8" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="AB8" s="17" t="s">
+      <c r="AG8" s="17" t="s">
         <v>324</v>
       </c>
-      <c r="AC8" s="2" t="s">
+      <c r="AH8" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="AD8" s="14" t="s">
+      <c r="AI8" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="AE8" s="14" t="s">
+      <c r="AJ8" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="AF8" s="13" t="s">
+      <c r="AK8" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="AG8" s="14" t="s">
+      <c r="AL8" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="AH8" s="15" t="s">
+      <c r="AM8" s="15" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2319,25 +2334,25 @@
       <c r="T9" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="AB9" s="17" t="s">
+      <c r="AG9" s="17" t="s">
         <v>325</v>
       </c>
-      <c r="AC9" s="2" t="s">
+      <c r="AH9" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="AD9" s="13" t="s">
+      <c r="AI9" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="AE9" s="14" t="s">
+      <c r="AJ9" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="AF9" s="14" t="s">
+      <c r="AK9" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="AG9" s="13" t="s">
+      <c r="AL9" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="AH9" s="14" t="s">
+      <c r="AM9" s="14" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2378,22 +2393,25 @@
       <c r="T10" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="AC10" s="2" t="s">
+      <c r="AG10" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AH10" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="AD10" s="15" t="s">
+      <c r="AI10" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="AE10" s="15" t="s">
+      <c r="AJ10" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="AF10" s="14" t="s">
+      <c r="AK10" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="AG10" s="13" t="s">
+      <c r="AL10" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="AH10" s="13" t="s">
+      <c r="AM10" s="13" t="s">
         <v>237</v>
       </c>
     </row>
@@ -2434,19 +2452,22 @@
       <c r="T11" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="AD11" s="15" t="s">
+      <c r="AH11" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="AI11" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="AE11" s="15" t="s">
+      <c r="AJ11" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="AF11" s="14" t="s">
+      <c r="AK11" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="AG11" s="13" t="s">
+      <c r="AL11" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AH11" s="14" t="s">
+      <c r="AM11" s="14" t="s">
         <v>174</v>
       </c>
     </row>
@@ -2487,16 +2508,16 @@
       <c r="T12" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="AD12" s="16" t="s">
+      <c r="AI12" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="AE12" s="14" t="s">
+      <c r="AJ12" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="AF12" s="15" t="s">
+      <c r="AK12" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="AG12" s="14" t="s">
+      <c r="AL12" s="14" t="s">
         <v>253</v>
       </c>
     </row>
@@ -2537,16 +2558,16 @@
       <c r="T13" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="AD13" s="15" t="s">
+      <c r="AI13" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="AE13" s="14" t="s">
+      <c r="AJ13" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="AF13" s="16" t="s">
+      <c r="AK13" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="AG13" s="13" t="s">
+      <c r="AL13" s="13" t="s">
         <v>304</v>
       </c>
     </row>
@@ -2587,13 +2608,13 @@
       <c r="T14" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="AD14" s="15" t="s">
+      <c r="AI14" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="AE14" s="16" t="s">
+      <c r="AJ14" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="AF14" s="14" t="s">
+      <c r="AK14" s="14" t="s">
         <v>300</v>
       </c>
     </row>
@@ -2634,13 +2655,13 @@
       <c r="T15" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="AD15" s="13" t="s">
+      <c r="AI15" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="AE15" s="15" t="s">
+      <c r="AJ15" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="AF15" s="14" t="s">
+      <c r="AK15" s="14" t="s">
         <v>302</v>
       </c>
     </row>
@@ -2672,7 +2693,7 @@
       <c r="T16" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="AF16" s="17" t="s">
+      <c r="AK16" s="17" t="s">
         <v>303</v>
       </c>
     </row>
